--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -13,8 +13,8 @@
     <sheet name="全卡表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能分类'!$B$4:$K$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'全卡表'!$B$4:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能分类'!$B$4:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'全卡表'!$B$4:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -517,7 +517,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒卡池 · 功能分类总览（v1.7，82 张）</t>
+          <t>赌徒卡池 · 功能分类总览（v1.8，78 张：起始 2 + 常规 76）</t>
         </is>
       </c>
     </row>
@@ -551,14 +551,14 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>赌博 6、击杀产金 5、风头·兑现 5、可变投入 4、真赌 4、特异 3、附加费 3、多掷 1、条件·赌博计数 1、自伤/自消耗 1、花费追踪 1、风头·只读条件 1</t>
+          <t>击杀产金 5、赌博 5、风头·兑现 5、可变投入 4、真赌 4、特异 3、附加费 3、条件·赌博计数 1、自伤/自消耗 1、花费追踪 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>即时产金 11、引擎产金 3、多掷 1、自伤/自消耗 1、赌博 1、风头·兑现 1</t>
+          <t>即时产金 10、引擎产金 3、自伤/自消耗 1、赌博 1、风头·兑现 1</t>
         </is>
       </c>
     </row>
@@ -587,14 +587,14 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.141025641025641</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>赌博 3、特异 2、自伤/自消耗 2、附加费 2、风头·兑现 2、多掷 1、花费追踪 1</t>
+          <t>赌博 3、特异 2、自伤/自消耗 2、附加费 2、风头·兑现 2、花费追踪 1</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1341463414634146</v>
+        <v>0.141025641025641</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="38" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>操控·辅助</t>
@@ -626,7 +626,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.08536585365853659</v>
+        <v>0.08974358974358974</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -659,14 +659,14 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>6 个功能族 / 82 张卡</t>
+          <t>6 个功能族 / 78 张卡</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -737,7 +737,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒卡池 · 逐卡功能分类（82 张，按功能族 / 机制排序）</t>
+          <t>赌徒卡池 · 逐卡功能分类（78 张，按功能族 / 机制排序）</t>
         </is>
       </c>
     </row>
@@ -1259,15 +1259,15 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>多掷</t>
+          <t>条件·赌博计数</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>满贯</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1282,27 +1282,27 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>2能+18金</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>赌博·多掷</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成 9 伤害 3 次，每击独立赌博：正面则该击改为 18 伤害。</t>
+          <t>花费 18 金币。
+造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>每击 10 / 正面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
+          <t>38 / 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1310,15 +1310,15 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>条件·赌博计数</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>满贯</t>
+          <t>打庄</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2能+18金</t>
+          <t>2能+15金</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1342,69 +1342,69 @@
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>花费 18 金币。
-造成 30 伤害。若本场战斗中你掷出过正面，改为 50 伤害。</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>38 / 62</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>打庄</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2能+15金</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>花费 15 金币。
 对生命值最低的敌人造成 43 伤害。</t>
         </is>
       </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>50 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>翻盘</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>1能+3金</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>花费 3 金币。
+造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>50 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
+          <t>14 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1416,92 +1416,92 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>翻盘</t>
+          <t>摊牌</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>至多 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>孤注一掷</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-造成 10 伤害。若你的生命低于 50%，改为 24 伤害。</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>摊牌</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+10金</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+          <t>花费 10 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>孤注一掷</t>
+          <t>押宝</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1能+10金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1546,13 +1546,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成 27 伤害。赌博：正面 → 改为造成 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害。</t>
+          <t>花费 5 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
+          <t>24 / 31</t>
         </is>
       </c>
     </row>
@@ -1568,142 +1568,141 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>押宝</t>
+          <t>押牌</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>12 / 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>真赌·自伤/自消耗</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>俄罗斯轮盘</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>连续下注</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>花费 5 金币。
-造成 18 伤害。赌博：反面 → 自己失去 6 点生命。</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>24 / 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>真赌</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>押牌</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>造成 8 伤害。赌博：正面 → 改为 15 伤害；反面 → 弃掉 2 张手牌。</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>真赌·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5 伤害；反面 → 其中 2 发改为打自己（自己共受 10 伤害）。</t>
+          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>额外 +6 伤害</t>
         </is>
       </c>
     </row>
@@ -1715,20 +1714,20 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>连续下注</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1738,22 +1737,22 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>9 / 正面 17</t>
         </is>
       </c>
     </row>
@@ -1769,16 +1768,16 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>买定离手</t>
+          <t>试手气</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1788,7 +1787,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -1798,12 +1797,12 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>对所有敌人造成 6 伤害。赌博：正面 → 改为造成 13 伤害。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>9 / 正面 17</t>
+          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1819,16 +1818,16 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>试手气</t>
+          <t>双倍下注</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1838,7 +1837,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1848,16 +1847,16 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>造成 5 伤害。赌博：正面 → 改为造成 10 伤害。</t>
+          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
+          <t>12 / 正面 12×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1869,11 +1868,11 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>双倍下注</t>
+          <t>翻本</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1888,7 +1887,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1898,16 +1897,17 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>造成 10 伤害。赌博：正面 → 改为造成 10 伤害两次。</t>
+          <t>花费 3 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>12 / 正面 12×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
+          <t>13 / 正面 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1919,11 +1919,11 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>翻本</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1948,13 +1948,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-造成 10 伤害。赌博：正面 → 改为造成 20 伤害。</t>
+          <t>花费 5 金币。
+硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>13 / 正面 25</t>
+          <t>5×3 / 正面每次 10</t>
         </is>
       </c>
     </row>
@@ -1966,20 +1966,20 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>连胜</t>
+          <t>底注</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1989,26 +1989,27 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>造成 5 伤害。赌博：正面 → 再次触发本效果并再次赌博（最多连锁 2 次）。</t>
+          <t>花费 2 金币。
+造成 10 伤害。</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>基础 7 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="54" customHeight="1">
+          <t>造成 13 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -2016,20 +2017,20 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>摇骰</t>
+          <t>看场</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2044,18 +2045,18 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
-对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9 伤害。</t>
+造成 16 伤害，施加 1 易伤。</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>19 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -2071,16 +2072,16 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>底注</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2090,7 +2091,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2100,13 +2101,13 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-造成 10 伤害。</t>
+          <t>花费 6 金币。
+造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>造成 13 伤害</t>
+          <t>9 点</t>
         </is>
       </c>
     </row>
@@ -2118,97 +2119,96 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>3能+12金</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>花费 12 金币。
+造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>46 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>花费 5 金币。
-造成 16 伤害，施加 1 易伤。</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>19 伤害，2 易伤</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>1能+6金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>花费 6 金币。
-造成 6 点无视格挡的伤害。</t>
+          <t>造成 6 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>9 伤害</t>
         </is>
       </c>
     </row>
@@ -2224,16 +2224,16 @@
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>同花顺</t>
+          <t>通杀</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>2能+5金</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2253,13 +2253,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>花费 12 金币。
-造成 43 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>花费 5 金币。
+对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>46 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -2275,16 +2275,16 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>乘胜</t>
+          <t>晒冷</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>3能+15金</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2304,12 +2304,13 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>造成 6 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>花费 15 金币。
+造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>9 伤害</t>
+          <t>62 伤害</t>
         </is>
       </c>
     </row>
@@ -2325,221 +2326,219 @@
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>通杀</t>
+          <t>追数</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>风头·续风</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>花费 8 金币。
+造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="38" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>风头·只读条件</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>叠注</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>花费 5 金币。
-对所有敌人造成 16 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>20 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>晒冷</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-造成 50 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>62 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="54" customHeight="1">
+          <t>10 / 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>风头·续风</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 29 伤害。风头正盛：数值随头顶倍率放大；若击杀则倍率不清空。</t>
+          <t>获得 5 金币。</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>36 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="38" customHeight="1">
+          <t>获得 7 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>叠注</t>
+          <t>筹码</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>获得 7 金币。</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>派彩</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 16 伤害。</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>10 / 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>本钱</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>起始</t>
-        </is>
-      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>技能</t>
@@ -2547,7 +2546,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>2能+3金</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2557,12 +2556,13 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>获得 5 金币。</t>
+          <t>花费 3 金币。
+获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币</t>
+          <t>获得 22 金币</t>
         </is>
       </c>
     </row>
@@ -2578,16 +2578,16 @@
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>筹码</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>获得 7 金币。</t>
+          <t>消耗手牌 1 张，获得 12 金币。</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>获得 16 金币</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2628,11 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>派彩</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2657,13 +2657,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-获得 18 金币，抽 1 张牌。</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>获得 22 金币</t>
+          <t>获得 18 金币</t>
         </is>
       </c>
     </row>
@@ -2679,16 +2678,16 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2708,16 +2707,16 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
+          <t>至多 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2729,16 +2728,16 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>高利贷</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2748,7 +2747,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2758,12 +2757,12 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
+          <t>每个敌人给予 5 金币。</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
@@ -2779,16 +2778,16 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>抽水</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2808,7 +2807,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
+          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2829,16 +2828,16 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2858,12 +2857,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币。</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
@@ -2875,115 +2874,115 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>每回合开始获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>至多 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>清码</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>每张 5 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>多掷·即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>老虎机</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -2993,28 +2992,27 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>2能+5金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>赌博·多掷</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-赌博 3 次，每次正面：获得 9 金币并抽 1 张牌。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>每次正面 11 金币</t>
+          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
@@ -3026,45 +3024,45 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>自伤/自消耗</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>返水</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>每回合开始获得 3 金币。</t>
+          <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>每回合 4 金币</t>
+          <t>抽 3 张，18 金币</t>
         </is>
       </c>
     </row>
@@ -3076,15 +3074,15 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>赌博·即时产金</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>抽头</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -3094,27 +3092,27 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>每回合 5 金币</t>
+          <t>9 / 正面 18</t>
         </is>
       </c>
     </row>
@@ -3126,165 +3124,166 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>利滚利</t>
+          <t>兑现</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>保底</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>12 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="38" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>保本</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>弃牌</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>抽 3 张，18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>赌博·即时产金</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>抽头</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币。赌博：正面 → 改为获得 14 金币。</t>
+          <t>花费 10 金币。
+消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>产金</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>自伤/自消耗</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>兑现</t>
+          <t>抵押</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3299,72 +3298,72 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>获得 12 格挡；自己失去 4 点生命。</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>16 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>点码</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>获得 7 金币（×风头正盛倍率，结算后清空倍率）。</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>获得 9 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>多掷</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>连庄</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>赌博·多掷</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>掷硬币 3 次，每次正面获得 8 格挡。</t>
+          <t>获得 5 格挡。本回合每花费过 5 金币，额外 +3 格挡。</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>每次 10</t>
+          <t>每 5 金 +4</t>
         </is>
       </c>
     </row>
@@ -3376,146 +3375,147 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 4 格挡。</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>6 / 正面 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="54" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>12 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="B57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>10 / 反面 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="54" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>保本</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>反水</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>花费 10 金币。
-消耗你一半金币，获得等量格挡（至多 30）。</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>至多 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
+          <t>花费 2 金币。
+硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
         </is>
       </c>
     </row>
@@ -3527,15 +3527,15 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>护盘</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3559,292 +3559,290 @@
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>获得 5 格挡。本回合每花费过 5 金币，额外 +3 格挡。</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>每 5 金 +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>盲注</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>获得 4 格挡。赌博：正面 → 改为获得 8 格挡。</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>6 / 正面 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="38" customHeight="1">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 8 格挡。赌博：反面 → 改为获得 16 格挡。</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="54" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 5 格挡。赌博：正面 → 改为 9 格挡并造成 9 伤害。</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>11 / 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>护盘</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>1能+4金</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 获得 15 格挡。</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
+    <row r="60" ht="38" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D60" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>护池</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>花费 4 金币。
 获得 5 格挡 3 次。</t>
         </is>
       </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>7 格挡 3 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>8 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="38" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现·自伤/自消耗</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>割肉</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>数牌</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>顶 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>弃置 1 张手牌，抽 2 张牌。</t>
+        </is>
+      </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>7 格挡 3 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="38" customHeight="1">
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>格挡</t>
+          <t>资源</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>收手</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3859,37 +3857,37 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>消耗 1 张手牌，抽 2 张牌。</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>8 格挡</t>
+          <t>抽 3 张</t>
         </is>
       </c>
     </row>
     <row r="66" ht="38" customHeight="1">
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>格挡</t>
+          <t>资源</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现·自伤/自消耗</t>
+          <t>真赌</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3909,17 +3907,17 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>获得 10 格挡。风头正盛：格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
@@ -3931,15 +3929,15 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>流水</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3949,112 +3947,112 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="38" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>加码</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>每 8 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="38" customHeight="1">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>洗牌</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>摸牌</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>弃置 1 张手牌，抽 2 张牌。</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>换牌</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4064,12 +4062,13 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>花费 5 金币。
+抽 3 张牌。</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>抽 4 张牌</t>
         </is>
       </c>
     </row>
@@ -4081,20 +4080,20 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4104,26 +4103,27 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+6金</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量。</t>
+          <t>花费 6 金币。
+获得 2 点能量。</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
+          <t>获得 3 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="38" customHeight="1">
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>资源</t>
@@ -4131,15 +4131,15 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>割禾青</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -4149,27 +4149,27 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>至多 4 张</t>
         </is>
       </c>
     </row>
@@ -4181,20 +4181,20 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
@@ -4231,20 +4231,20 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·只读条件</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>摸牌</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4264,38 +4264,37 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-抽 3 张牌。</t>
+          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>抽 4 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="38" customHeight="1">
+          <t>抽 3 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>操控·辅助</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>做局</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>暗记</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4305,7 +4304,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>0能+6金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4315,33 +4314,32 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>花费 6 金币。
-获得 2 点能量。</t>
+          <t>你的接下来 1 次赌博必为正面。</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>获得 3 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="38" customHeight="1">
+          <t>接下来 2 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>操控·辅助</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>做局</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>手气正旺</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -4351,114 +4349,114 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>赌神</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>3能</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>你的所有赌博视为正面。</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>费用变为 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>叠码</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。风头正盛：结算后清空倍率。</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>至多 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>79</v>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>换筹</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>按风头正盛倍率折算：获得「倍率取整」点能量（+0），结算后清空倍率。</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>+1 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="38" customHeight="1">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>风头·只读条件</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>底牌</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -4466,12 +4464,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
@@ -4487,16 +4485,16 @@
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>暗记</t>
+          <t>出千</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4506,7 +4504,7 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4516,12 +4514,12 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>你的接下来 1 次赌博必为正面。</t>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>接下来 2 次必为正面</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4537,21 +4535,21 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>手气正旺</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4566,12 +4564,12 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+          <t>你的风头倍率翻倍（不清空）。</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4583,72 +4581,72 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>做局</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>赌神</t>
+          <t>假筹</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>本场战斗前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="38" customHeight="1">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>抽佣</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面。</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>叠码</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
           <t>技能</t>
@@ -4656,7 +4654,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4665,270 +4663,70 @@
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>倍率 +1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>出千</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>倍投</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>假筹</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="38" customHeight="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>debuff</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>抽佣</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>花费 8 金币。
 施加 5 点力量削弱与 3 易伤。</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>6 点力量削弱与 4 易伤</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="38" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
+    <row r="82" ht="38" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D86" s="11" t="n">
+      <c r="D82" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>放水</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>花费 4 金币。
 施加 4 虚弱。</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>施加 5 虚弱</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:K86"/>
+  <autoFilter ref="B4:K82"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K2"/>
   </mergeCells>
@@ -5074,11 +4872,9 @@
         <v>4</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n">
         <v>4</v>
       </c>
@@ -5107,7 +4903,7 @@
         <v>3</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -5121,9 +4917,7 @@
       <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="11" t="n"/>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n">
         <v>1</v>
@@ -5132,7 +4926,7 @@
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>3</v>
@@ -5144,7 +4938,7 @@
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5160,9 +4954,7 @@
       <c r="E7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n">
         <v>2</v>
@@ -5183,7 +4975,7 @@
         <v>2</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5294,10 +5086,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>5</v>
@@ -5315,7 +5107,7 @@
         <v>5</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
@@ -5333,14 +5125,14 @@
         <v>10</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1"/>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、老虎机、抽头、割肉），故机制列合计 86 &gt; 卡数 82；「合计」列为各功能族实际张数，总计 82。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、抽头、割肉），故机制列合计 81 &gt; 卡数 78；「合计」列为各功能族实际张数，总计 78。</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5377,7 +5169,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒全卡表（82 张，按档位 / 编号排序）</t>
+          <t>赌徒全卡表（78 张，按档位 / 编号排序）</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5287,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>造成 5 伤害。赌博：正面 → 改为造成 10 伤害。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5617,7 +5409,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>对所有敌人造成 6 伤害。赌博：正面 → 改为造成 13 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -5788,7 +5580,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="38" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>普通</t>
@@ -5819,7 +5611,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>获得 4 格挡。赌博：正面 → 改为获得 8 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 4 格挡。</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -5950,7 +5742,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>普通</t>
@@ -5981,7 +5773,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>获得 5 格挡。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -5990,7 +5782,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>普通</t>
@@ -6021,7 +5813,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>造成 6 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>造成 6 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -6466,7 +6258,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>造成 10 伤害。赌博：正面 → 改为造成 10 伤害两次。</t>
+          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -6506,7 +6298,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 16 伤害。</t>
+          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6515,7 +6307,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1">
+    <row r="32" ht="54" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -6547,7 +6339,7 @@
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
-造成 10 伤害。赌博：正面 → 改为造成 20 伤害。</t>
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -6556,18 +6348,18 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1">
+    <row r="33" ht="54" customHeight="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>连胜</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -6577,78 +6369,78 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>花费 5 金币。
+硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>5×3 / 正面每次 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>暗记</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>造成 5 伤害。赌博：正面 → 再次触发本效果并再次赌博（最多连锁 2 次）。</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>基础 7 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次赌博必为正面。</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>接下来 2 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>花费 5 金币。
-对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9 伤害。</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>5×3 / 正面每次 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
       <c r="C35" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>暗记</t>
+          <t>派彩</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -6658,7 +6450,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+3金</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -6667,54 +6459,54 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次赌博必为正面。</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>接下来 2 次必为正面</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>派彩</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2能+3金</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
 获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>获得 22 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>数牌</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+        </is>
+      </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>获得 22 金币</t>
+          <t>顶 4 张</t>
         </is>
       </c>
     </row>
@@ -6725,11 +6517,11 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -6739,423 +6531,424 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>消耗手牌 1 张，获得 12 金币。</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>获得 16 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>抽头</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>9 / 正面 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>10 / 反面 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>本场战斗前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>高利贷</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>获得 18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>兑筹</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="C42" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>割禾青</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>至多 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>兑现</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>抽头</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>获得 7 金币。赌博：正面 → 改为获得 14 金币。</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>9 / 正面 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 8 格挡。赌博：反面 → 改为获得 16 格挡。</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>假筹</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>高利贷</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>流水</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>每累计 8 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="38" customHeight="1">
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>割禾青</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="C47" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2能+5金</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。风头正盛：结算后清空倍率。</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>至多 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>兑现</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币（×风头正盛倍率，结算后清空倍率）。</t>
+          <t>花费 5 金币。
+对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -7166,11 +6959,11 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>通杀</t>
+          <t>再加注</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -7180,212 +6973,211 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2能+5金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
+          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>抽水</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>至多 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>押宝</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
           <t>花费 5 金币。
-对所有敌人造成 16 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>20 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="54" customHeight="1">
-      <c r="B49" s="3" t="inlineStr">
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>再加注</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C51" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>反水</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>叠码</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>12 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>倍率 +1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="38" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>抽水</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="C53" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>保底</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>至多 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>押宝</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>花费 5 金币。
-造成 18 伤害。赌博：反面 → 自己失去 6 点生命。</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>24 / 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="54" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 5 格挡。赌博：正面 → 改为 9 格挡并造成 9 伤害。</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>11 / 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>叠码</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -7393,12 +7185,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -7409,11 +7201,11 @@
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -7433,27 +7225,27 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
+          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>12 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="38" customHeight="1">
+          <t>每 8 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7473,37 +7265,37 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>每 8 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
+          <t>每张 5 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="54" customHeight="1">
       <c r="B56" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>翻盘</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -7513,27 +7305,28 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+          <t>花费 3 金币。
+造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="54" customHeight="1">
+          <t>14 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="38" customHeight="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>翻盘</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7543,7 +7336,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -7552,55 +7345,54 @@
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-造成 10 伤害。若你的生命低于 50%，改为 24 伤害。</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="38" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>花费 6 金币。
 造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>9 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>获得 12 格挡；自己失去 4 点生命。</t>
+        </is>
+      </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>16 格挡</t>
         </is>
       </c>
     </row>
@@ -7611,11 +7403,11 @@
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>连庄</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7625,117 +7417,118 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，抽 2 张牌。</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="54" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>孤注一掷</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>1能+10金</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>花费 10 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>正面 50 / 反面 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="54" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>俄罗斯轮盘</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>赌博·多掷</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>掷硬币 3 次，每次正面获得 8 格挡。</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>每次 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>16 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>换牌</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="54" customHeight="1">
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="38" customHeight="1">
       <c r="B62" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>孤注一掷</t>
+          <t>爆机</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -7745,38 +7538,38 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>1能+10金</t>
+          <t>3能+8金</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成 27 伤害。赌博：正面 → 改为造成 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害。</t>
+          <t>花费 8 金币。
+造成 35 伤害。击杀则获得 25 金币。</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="54" customHeight="1">
+          <t>40 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="38" customHeight="1">
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>俄罗斯轮盘</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7786,22 +7579,23 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5 伤害；反面 → 其中 2 发改为打自己（自己共受 10 伤害）。</t>
+          <t>花费 12 金币。
+造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>46 伤害</t>
         </is>
       </c>
     </row>
@@ -7812,119 +7606,117 @@
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>爆机</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>正面 5 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="38" customHeight="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>打庄</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>3能+8金</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>花费 8 金币。
-造成 35 伤害。击杀则获得 25 金币。</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>40 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="54" customHeight="1">
-      <c r="B65" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>2能+15金</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>花费 15 金币。
+对生命值最低的敌人造成 43 伤害。</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>50 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>赌博·多掷</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>花费 10 金币。
-造成 9 伤害 3 次，每击独立赌博：正面则该击改为 18 伤害。</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>每击 10 / 正面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="54" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
       <c r="C66" s="11" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>同花顺</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>花费 12 金币。
-造成 43 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
+          <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>46 伤害</t>
+          <t>抽 3 张，18 金币</t>
         </is>
       </c>
     </row>
@@ -7935,11 +7727,11 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>抽佣</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -7949,22 +7741,23 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量。</t>
+          <t>花费 8 金币。
+施加 5 点力量削弱与 3 易伤。</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>6 点力量削弱与 4 易伤</t>
         </is>
       </c>
     </row>
@@ -7975,11 +7768,11 @@
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>老虎机</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -7989,48 +7782,47 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2能+5金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>赌博·多掷</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-赌博 3 次，每次正面：获得 9 金币并抽 1 张牌。</t>
+          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>每次正面 11 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="38" customHeight="1">
+          <t>抽 3 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
       <c r="B69" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>打庄</t>
+          <t>赌神</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -8040,13 +7832,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-对生命值最低的敌人造成 43 伤害。</t>
+          <t>你的所有赌博视为正面。</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>50 伤害</t>
+          <t>费用变为 2</t>
         </is>
       </c>
     </row>
@@ -8057,16 +7848,16 @@
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>弃牌</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -8076,17 +7867,17 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
@@ -8097,239 +7888,239 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>抽佣</t>
+          <t>晒冷</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>3能+15金</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>花费 15 金币。
+造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>62 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="54" customHeight="1">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>追数</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>风头·续风</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>花费 8 金币。
+造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="38" customHeight="1">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>割肉</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>花费 8 金币。
-施加 5 点力量削弱与 3 易伤。</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>6 点力量削弱与 4 易伤</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="38" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="38" customHeight="1">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>底牌</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="C74" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>全下</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>X能+7×X金</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>花费 7×X 金币。
+对随机敌人造成 9×X 伤害，共 X 次。</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>金币费降为 5×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>出千</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>抽 3 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="38" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C73" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面。</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>利滚利</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="C76" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="54" customHeight="1">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>晒冷</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>3能+15金</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>花费 15 金币。
-造成 50 伤害。风头正盛：数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>62 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="54" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>追数</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>风头·续风</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 29 伤害。风头正盛：数值随头顶倍率放大；若击杀则倍率不清空。</t>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>至多 28</t>
         </is>
       </c>
     </row>
@@ -8340,11 +8131,11 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>保本</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -8354,22 +8145,23 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡。风头正盛：格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+          <t>花费 10 金币。
+消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
@@ -8380,11 +8172,11 @@
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>全下</t>
+          <t>押牌</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -8394,103 +8186,103 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>X能+7×X金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>花费 7×X 金币。
-对随机敌人造成 9×X 伤害，共 X 次。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>金币费降为 5×X</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
+          <t>12 / 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="54" customHeight="1">
       <c r="B79" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>截胡</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>花费 8 金币。
+对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>26 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>倍投</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>你的风头倍率翻倍（不清空）。</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>费用变为 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="38" customHeight="1">
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>摊牌</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>至多 28</t>
         </is>
       </c>
     </row>
@@ -8501,11 +8293,11 @@
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>保本</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -8515,38 +8307,37 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-消耗你一半金币，获得等量格挡（至多 30）。</t>
+          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>至多 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="38" customHeight="1">
+          <t>+1 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="54" customHeight="1">
       <c r="B82" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>满贯</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -8556,189 +8347,28 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+18金</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 改为 15 伤害；反面 → 弃掉 2 张手牌。</t>
+          <t>花费 18 金币。
+造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="54" customHeight="1">
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>截胡</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>花费 8 金币。
-对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>26 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>倍投</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="38" customHeight="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>换筹</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>按风头正盛倍率折算：获得「倍率取整」点能量（+0），结算后清空倍率。</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>+1 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="54" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>满贯</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>2能+18金</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>花费 18 金币。
-造成 30 伤害。若本场战斗中你掷出过正面，改为 50 伤害。</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
           <t>38 / 62</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:I86"/>
+  <autoFilter ref="B4:I82"/>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -13,8 +13,8 @@
     <sheet name="全卡表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能分类'!$B$4:$K$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'全卡表'!$B$4:$I$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能分类'!$B$4:$K$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'全卡表'!$B$4:$I$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -551,18 +551,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>击杀产金 5、赌博 5、风头·兑现 5、可变投入 4、真赌 4、特异 3、附加费 3、条件·赌博计数 1、自伤/自消耗 1、花费追踪 1、风头·只读条件 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
+          <t>赌博 6、击杀产金 5、风头·兑现 5、可变投入 4、真赌 4、特异 3、附加费 3、出千·确定性 2、自伤/自消耗 2、赌命·血线 2、条件·赌博计数 1、花费追踪 1、风头·只读条件 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -572,7 +572,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.141025641025641</v>
+        <v>0.1264367816091954</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -605,32 +605,32 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>特异 3、花费追踪 2、附加费 2、风头·兑现 2、真赌 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0.141025641025641</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>特异 3、花费追踪 2、附加费 2、风头·兑现 2、真赌 1、风头·只读条件 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D9" s="4" t="n">
-        <v>0.08974358974358974</v>
+        <v>0.1264367816091954</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>做局 6、特异 1</t>
+          <t>做局 6、出千·确定性 3、特异 1、赌命·血线 1</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.02298850574712644</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -659,14 +659,14 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>6 个功能族 / 78 张卡</t>
+          <t>6 个功能族 / 87 张卡</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -737,7 +737,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒卡池 · 逐卡功能分类（78 张，按功能族 / 机制排序）</t>
+          <t>赌徒卡池 · 逐卡功能分类（87 张，按功能族 / 机制排序）</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="38" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -802,907 +802,907 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>收网</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>消耗你所有的必正次数，每消耗 1 次造成 9 伤害（没有必正时无事发生）。</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>每次 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>击杀产金</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>悬红</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>造成 7 伤害。击杀则获得 10 金币。</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>9 伤害，击杀 +14 金</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>击杀产金</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>清台</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>造成 15 伤害</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>击杀产金</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>爆机</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>3能+8金</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 造成 35 伤害。击杀则获得 25 金币。</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>40 伤害</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>击杀产金</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>吃水</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 造成 12 伤害；溢出的伤害转为金币。</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>16 伤害</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>击杀产金</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>截胡</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>26 伤害</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>可变投入</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>加注</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>花费至多 6 金币，每 1 金币 +2 伤害。
 造成 6 伤害。</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>基础 8 伤害</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="12" ht="38" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>可变投入</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>梭哈</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>X能+10×X金</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>花费 10×X 金币。
 造成 27×X 伤害。</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>金币费降为 8×X</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>可变投入</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>再加注</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>12 伤害</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>可变投入</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>全下</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>X能+7×X金</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>花费 7×X 金币。
 对随机敌人造成 9×X 伤害，共 X 次。</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>金币费降为 5×X</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>条件·赌博计数</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>满贯</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>2能+18金</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>花费 18 金币。
 造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>38 / 62</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>打庄</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>2能+15金</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>花费 15 金币。
 对生命值最低的敌人造成 43 伤害。</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>50 伤害</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>翻盘</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>14 / 30</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>摊牌</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>至多 28</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>真赌</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D19" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>孤注一掷</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>1能+10金</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>花费 10 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>真赌</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D20" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>押宝</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>24 / 31</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21" ht="38" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>真赌</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D21" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>押牌</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>12 / 19</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>真赌·自伤/自消耗</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D22" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>俄罗斯轮盘</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>每次 4 / 正面 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>花费追踪</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>连续下注</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>额外 +6 伤害</t>
         </is>
       </c>
     </row>
@@ -1714,15 +1714,15 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>自伤/自消耗·赌命·血线</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>买定离手</t>
+          <t>放血</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>造成 9 伤害。自己失去 3 点生命。</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>9 / 正面 17</t>
+          <t>造成 12 伤害</t>
         </is>
       </c>
     </row>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>试手气</t>
+          <t>连续下注</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
+          <t>额外 +6 伤害</t>
         </is>
       </c>
     </row>
@@ -1818,951 +1818,952 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>买定离手</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>9 / 正面 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>试手气</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>起始</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>双倍下注</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>12 / 正面 12×2</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="28" ht="54" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D28" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>翻本</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>13 / 正面 25</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="29" ht="54" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D29" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>摇骰</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>5×3 / 正面每次 10</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+    <row r="30" ht="38" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>赌博·出千·确定性</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>赌命·血线</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>花费 10 金币。
+造成等于「你已失去生命」的 50% 的伤害。</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>底注</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>1能+2金</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>花费 2 金币。
 造成 10 伤害。</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>造成 13 伤害</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="33" ht="38" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>看场</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 造成 16 伤害，施加 1 易伤。</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>19 伤害，2 易伤</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
+    <row r="34" ht="38" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D34" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>暗注</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>1能+6金</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>花费 6 金币。
 造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>9 点</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="35" ht="38" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D35" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>同花顺</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>3能+12金</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>花费 12 金币。
 造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>46 伤害</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D36" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>乘胜</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>造成 6 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>9 伤害</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="37" ht="54" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D37" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>通杀</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>2能+5金</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>20 伤害</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="38" ht="38" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D38" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>晒冷</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>3能+15金</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>花费 15 金币。
 造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>62 伤害</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="54" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="39" ht="54" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D39" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>追数</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>风头·续风</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>花费 8 金币。
 造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>36 伤害</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
+    <row r="40" ht="38" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>风头·只读条件</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D40" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>叠注</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>10 / 20</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>即时产金</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D41" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>本钱</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>起始</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>获得 5 金币。</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>获得 7 金币</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>即时产金</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D42" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>筹码</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>获得 7 金币。</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>获得 9 金币</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="43" ht="38" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>即时产金</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D43" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>派彩</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>2能+3金</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>获得 22 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>兑筹</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>高利贷</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>散码</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>至多 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>买码</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>每个敌人给予 5 金币。</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
@@ -2778,11 +2779,11 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2807,16 +2808,16 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
+          <t>消耗手牌 1 张，获得 12 金币。</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>至多 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
+          <t>获得 16 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2828,11 +2829,11 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2847,7 +2848,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2857,12 +2858,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>获得 18 金币</t>
         </is>
       </c>
     </row>
@@ -2874,15 +2875,15 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>返水</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -2892,7 +2893,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2907,16 +2908,16 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>每回合开始获得 3 金币。</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>每回合 4 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="38" customHeight="1">
+          <t>至多 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2924,30 +2925,30 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2957,12 +2958,12 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+          <t>每个敌人给予 5 金币。</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>每回合 5 金币</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
@@ -2974,30 +2975,30 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>利滚利</t>
+          <t>抽水</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3007,12 +3008,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
@@ -3024,825 +3025,825 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>清码</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>每张 5 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>返水</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>每回合开始获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>利滚利</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
           <t>自伤/自消耗</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D53" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>弃牌</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>消耗</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>抽 3 张，18 金币</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+    <row r="54" ht="38" customHeight="1">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>赌博·即时产金</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D54" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>抽头</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>9 / 正面 18</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D55" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>兑现</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>获得 9 金币</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
+    <row r="56" ht="38" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D56" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>保底</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>12 格挡</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="38" customHeight="1">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="57" ht="38" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D57" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>保本</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>2能+10金</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>花费 10 金币。
 消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>至多 40</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="B54" s="5" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>自伤/自消耗</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D58" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>抵押</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>获得 12 格挡；自己失去 4 点生命。</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>16 格挡</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="38" customHeight="1">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="59" ht="38" customHeight="1">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>花费追踪</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D59" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>点码</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>获得 5 格挡。本回合每花费过 5 金币，额外 +3 格挡。</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>每 5 金 +4</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
+    <row r="60" ht="38" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D60" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>盲注</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 4 格挡。</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>6 / 正面 13</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="54" customHeight="1">
-      <c r="B57" s="3" t="inlineStr">
+    <row r="61" ht="54" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n">
+      <c r="D61" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>保险</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>1能+2金</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>10 / 反面 20</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="54" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
+    <row r="62" ht="54" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D62" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>反水</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>1能+2金</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="38" customHeight="1">
-      <c r="B59" s="3" t="inlineStr">
+    <row r="63" ht="38" customHeight="1">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n">
+      <c r="D63" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>护盘</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 获得 15 格挡。</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="38" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
+    <row r="64" ht="38" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D64" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>护池</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>花费 4 金币。
 获得 5 格挡 3 次。</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>7 格挡 3 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>收手</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>割肉</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>13 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>数牌</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>洗牌</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>弃置 1 张手牌，抽 2 张牌。</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>换牌</t>
+          <t>收手</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3857,37 +3858,37 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>8 格挡</t>
         </is>
       </c>
     </row>
     <row r="66" ht="38" customHeight="1">
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>风头·兑现·自伤/自消耗</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>割肉</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3907,17 +3908,17 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>13 格挡</t>
         </is>
       </c>
     </row>
@@ -3929,597 +3930,597 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>数牌</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>顶 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>弃置 1 张手牌，抽 2 张牌。</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>换牌</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，抽 2 张牌。</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>单双</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>正面 5 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="38" customHeight="1">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>自伤/自消耗·赌命·血线</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>血本</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>失去 5 点生命。获得 2 点能量。</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>失去 4 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
           <t>花费追踪</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n">
+      <c r="D72" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>流水</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>你每累计花费 10 金币，抽 1 张牌。</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>每累计 8 金币</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="38" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+    <row r="73" ht="38" customHeight="1">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>花费追踪</t>
         </is>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D73" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>加码</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>每 8 金</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="38" customHeight="1">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="74" ht="38" customHeight="1">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n">
+      <c r="D74" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>摸牌</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 抽 3 张牌。</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>抽 4 张牌</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="38" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
+    <row r="75" ht="38" customHeight="1">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D75" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>换码</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>0能+6金</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
 获得 2 点能量。</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>获得 3 点</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="76" ht="38" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n">
+      <c r="D76" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>割禾青</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>至多 4 张</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="38" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
+    <row r="77" ht="38" customHeight="1">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D77" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>换筹</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>+1 点</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="38" customHeight="1">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="78" ht="38" customHeight="1">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>风头·只读条件</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n">
+      <c r="D78" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>底牌</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr">
         <is>
           <t>抽 3 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>暗记</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次赌博必为正面。</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>接下来 2 次必为正面</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面。</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>叠码</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>倍率 +1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>出千</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4535,16 +4536,16 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>倍投</t>
+          <t>暗记</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -4554,7 +4555,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4564,12 +4565,12 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
+          <t>你的接下来 2 次赌博必为正面。</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>接下来 3 次必为正面</t>
         </is>
       </c>
     </row>
@@ -4581,152 +4582,603 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>赌神</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>3能</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>你的所有赌博视为正面。</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>叠码</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>倍率 +1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>出千</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>倍投</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>你的风头倍率翻倍（不清空）。</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>封口</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>获得 1 次必正，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>获得 2 次必正</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>千王</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="38" customHeight="1">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>花费 6 金币。
+本回合你接下来的 3 次赌博必为正面。</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D80" s="11" t="n">
+      <c r="D88" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>假筹</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>你的接下来 1 次金币花费不消耗金币。</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>本场战斗前 2 次</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="38" customHeight="1">
-      <c r="B81" s="3" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>赌命·血线</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>押注</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="38" customHeight="1">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D81" s="10" t="n">
+      <c r="D90" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>抽佣</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 施加 5 点力量削弱与 3 易伤。</t>
         </is>
       </c>
-      <c r="K81" s="3" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t>6 点力量削弱与 4 易伤</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="38" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
+    <row r="91" ht="38" customHeight="1">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>附加费</t>
         </is>
       </c>
-      <c r="D82" s="11" t="n">
+      <c r="D91" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>放水</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 施加 4 虚弱。</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>施加 5 虚弱</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:K82"/>
+  <autoFilter ref="B4:K91"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K2"/>
   </mergeCells>
@@ -4740,7 +5192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4761,6 +5213,8 @@
     <col width="8" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -4855,6 +5309,16 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>赌命·血线</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
@@ -4872,7 +5336,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n">
@@ -4897,13 +5361,19 @@
         <v>1</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -4937,7 +5407,9 @@
         <v>1</v>
       </c>
       <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4974,7 +5446,9 @@
       <c r="Q7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5007,12 +5481,18 @@
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="n"/>
+      <c r="P8" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="11" t="n">
-        <v>11</v>
+      <c r="R8" s="11" t="n"/>
+      <c r="S8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -5041,7 +5521,13 @@
         <v>1</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="S9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -5069,7 +5555,9 @@
       <c r="Q10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" s="11" t="n"/>
+      <c r="S10" s="11" t="n"/>
+      <c r="T10" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5086,7 +5574,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>0</v>
@@ -5119,27 +5607,33 @@
         <v>1</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="7" t="n">
         <v>10</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>78</v>
+        <v>5</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1"/>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、抽头、割肉），故机制列合计 81 &gt; 卡数 78；「合计」列为各功能族实际张数，总计 78。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、放血、偷天换日、抽头、割肉、血本），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="B13:T13"/>
+    <mergeCell ref="B2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5151,7 +5645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5169,7 +5663,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒全卡表（78 张，按档位 / 编号排序）</t>
+          <t>赌徒全卡表（87 张，按档位 / 编号排序）</t>
         </is>
       </c>
     </row>
@@ -6105,689 +6599,689 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="38" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>封口</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>获得 1 次必正，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>获得 2 次必正</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>血本</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>失去 5 点生命。获得 2 点能量。</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>失去 4 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>放血</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>造成 9 伤害。自己失去 3 点生命。</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>造成 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C31" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>梭哈</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>X能+10×X金</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>花费 10×X 金币。
 造成 27×X 伤害。</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>金币费降为 8×X</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+    <row r="32" ht="38" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C32" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>连续下注</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>额外 +6 伤害</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="33" ht="54" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C33" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>清台</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>1能+4金</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>花费 4 金币。
 对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>造成 15 伤害</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
+    <row r="34" ht="38" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C34" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>双倍下注</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>12 / 正面 12×2</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="35" ht="38" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C35" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>叠注</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>10 / 20</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="36" ht="54" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C36" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>翻本</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>13 / 正面 25</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="37" ht="54" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C37" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>摇骰</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>5×3 / 正面每次 10</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>暗记</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次赌博必为正面。</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>接下来 2 次必为正面</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="38" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>你的接下来 2 次赌博必为正面。</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>接下来 3 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C39" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>派彩</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>2能+3金</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>获得 22 金币</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C40" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>数牌</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>顶 4 张</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C41" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>兑筹</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>消耗手牌 1 张，获得 12 金币。</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>获得 16 金币</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="42" ht="38" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C42" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>抽头</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>9 / 正面 18</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="43" ht="54" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C43" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>保险</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>1能+2金</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>假筹</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>高利贷</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
         </is>
       </c>
     </row>
@@ -6798,16 +7292,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>假筹</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -6822,12 +7316,12 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>本场战斗前 2 次</t>
         </is>
       </c>
     </row>
@@ -6838,11 +7332,11 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6857,17 +7351,17 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>至多 4 张</t>
+          <t>获得 18 金币</t>
         </is>
       </c>
     </row>
@@ -6878,1497 +7372,1859 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>割禾青</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>至多 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>兑现</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>获得 9 金币</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="54" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="51" ht="54" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C51" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>通杀</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>2能+5金</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>20 伤害</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="54" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
+    <row r="52" ht="54" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C52" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>再加注</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>12 伤害</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="3" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C53" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>抽水</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>每张手牌获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>至多 12</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="54" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C54" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>押宝</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1能+5金</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>24 / 31</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="54" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="55" ht="54" customHeight="1">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C55" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>反水</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>1能+2金</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C56" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>叠码</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>你的风头倍率 +0.5 ×2（不清空）。</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="38" customHeight="1">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="57" ht="38" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C57" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>保底</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>12 格挡</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="38" customHeight="1">
-      <c r="B54" s="5" t="inlineStr">
+    <row r="58" ht="38" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C58" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>加码</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>每 8 金</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C59" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>清码</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>每张 5 金</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="54" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
+    <row r="60" ht="54" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C56" s="11" t="n">
+      <c r="C60" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>翻盘</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
 造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>14 / 30</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="B57" s="3" t="inlineStr">
+    <row r="61" ht="38" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C61" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>暗注</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>1能+6金</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
 造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>9 点</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C62" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>抵押</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>获得 12 格挡；自己失去 4 点生命。</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>16 格挡</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="B59" s="3" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C63" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>换牌</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>消耗 1 张手牌，抽 2 张牌。</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>抽 3 张</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="54" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
+    <row r="64" ht="38" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>收网</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>消耗你所有的必正次数，每消耗 1 次造成 9 伤害（没有必正时无事发生）。</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>每次 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>押注</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="54" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C66" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>孤注一掷</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1能+10金</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="54" customHeight="1">
-      <c r="B61" s="3" t="inlineStr">
+    <row r="67" ht="54" customHeight="1">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C67" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>俄罗斯轮盘</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>每次 4 / 正面 6</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
+    <row r="68" ht="38" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C62" s="11" t="n">
+      <c r="C68" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>爆机</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>3能+8金</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 造成 35 伤害。击杀则获得 25 金币。</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>40 伤害</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="B63" s="3" t="inlineStr">
+    <row r="69" ht="38" customHeight="1">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C69" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>同花顺</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>3能+12金</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>花费 12 金币。
 造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>46 伤害</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
+    <row r="70" ht="38" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C70" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>单双</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="38" customHeight="1">
-      <c r="B65" s="3" t="inlineStr">
+    <row r="71" ht="38" customHeight="1">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C71" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>打庄</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>2能+15金</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>花费 15 金币。
 对生命值最低的敌人造成 43 伤害。</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>50 伤害</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C66" s="11" t="n">
+      <c r="C72" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>弃牌</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>消耗</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>抽 3 张，18 金币</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="38" customHeight="1">
-      <c r="B67" s="3" t="inlineStr">
+    <row r="73" ht="38" customHeight="1">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C73" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>抽佣</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>花费 8 金币。
 施加 5 点力量削弱与 3 易伤。</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>6 点力量削弱与 4 易伤</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="38" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+    <row r="74" ht="38" customHeight="1">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C68" s="11" t="n">
+      <c r="C74" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>底牌</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C75" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>赌神</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>3能</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>你的所有赌博视为正面。</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>费用变为 2</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C70" s="11" t="n">
+      <c r="C76" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>利滚利</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>额外 3 金币</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="77" ht="38" customHeight="1">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C77" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>晒冷</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>3能+15金</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>花费 15 金币。
 造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>62 伤害</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="54" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
+    <row r="78" ht="54" customHeight="1">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C72" s="11" t="n">
+      <c r="C78" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>追数</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>风头·续风</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>36 伤害</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="38" customHeight="1">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="79" ht="38" customHeight="1">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C73" s="10" t="n">
+      <c r="C79" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>割肉</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>13 格挡</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="38" customHeight="1">
-      <c r="B74" s="5" t="inlineStr">
+    <row r="80" ht="38" customHeight="1">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C74" s="11" t="n">
+      <c r="C80" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>全下</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>X能+7×X金</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>花费 7×X 金币。
 对随机敌人造成 9×X 伤害，共 X 次。</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>金币费降为 5×X</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="3" t="inlineStr">
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C81" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>出千</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>你接下来的所有赌博必为正面（本回合）。</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>费用变为 1</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
+    <row r="82" ht="38" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C76" s="11" t="n">
+      <c r="C82" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>摊牌</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>至多 28</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="38" customHeight="1">
-      <c r="B77" s="3" t="inlineStr">
+    <row r="83" ht="38" customHeight="1">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n">
+      <c r="C83" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>保本</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>2能+10金</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>花费 10 金币。
 消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>至多 40</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="38" customHeight="1">
-      <c r="B78" s="5" t="inlineStr">
+    <row r="84" ht="38" customHeight="1">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C78" s="11" t="n">
+      <c r="C84" s="11" t="n">
         <v>76</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>押牌</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>12 / 19</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="54" customHeight="1">
-      <c r="B79" s="3" t="inlineStr">
+    <row r="85" ht="54" customHeight="1">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C85" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>截胡</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>花费 8 金币。
 对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>26 伤害</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="B80" s="5" t="inlineStr">
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C80" s="11" t="n">
+      <c r="C86" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>倍投</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>你的风头倍率翻倍（不清空）。</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>费用变为 1</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="38" customHeight="1">
-      <c r="B81" s="3" t="inlineStr">
+    <row r="87" ht="38" customHeight="1">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n">
+      <c r="C87" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>换筹</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>+1 点</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="54" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
+    <row r="88" ht="54" customHeight="1">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="C82" s="11" t="n">
+      <c r="C88" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>满贯</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>2能+18金</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>花费 18 金币。
 造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>38 / 62</t>
         </is>
       </c>
     </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>千王</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="38" customHeight="1">
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>花费 6 金币。
+本回合你接下来的 3 次赌博必为正面。</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="38" customHeight="1">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>花费 10 金币。
+造成等于「你已失去生命」的 50% 的伤害。</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B4:I82"/>
+  <autoFilter ref="B4:I91"/>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -551,32 +551,32 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.4022988505747127</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>赌博 6、击杀产金 5、风头·兑现 5、可变投入 4、真赌 4、特异 3、附加费 3、出千·确定性 2、自伤/自消耗 2、赌命·血线 2、条件·赌博计数 1、花费追踪 1、风头·只读条件 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+          <t>赌博 6、风头·兑现 5、击杀产金 4、真赌 4、可变投入 3、特异 3、附加费 3、出千·确定性 2、花费追踪 2、即时产金 1、条件·赌博计数 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>即时产金 10、引擎产金 3、自伤/自消耗 1、赌博 1、风头·兑现 1</t>
+          <t>即时产金 10、引擎产金 3、自伤/自消耗 2、赌命·血线 1、赌博 1、风头·兑现 1</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>特异 3、花费追踪 2、附加费 2、风头·兑现 2、真赌 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
+          <t>特异 3、花费追踪 2、附加费 2、风头·兑现 2、即时产金 1、真赌 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。击杀则获得 10 金币。</t>
+          <t>造成 9 伤害。击杀则获得 15 金币。</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>9 伤害，击杀 +14 金</t>
+          <t>11 伤害，击杀 +19 金</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>截胡</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1036,65 +1036,65 @@
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>花费 4 金币。
-造成 12 伤害；溢出的伤害转为金币。</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>16 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>击杀产金</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>截胡</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
         </is>
       </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>26 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>吃水</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>1能+3金</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>花费 3 金币。
+造成 16 伤害；被格挡抵消的伤害转为金币。</t>
+        </is>
+      </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>加注</t>
+          <t>梭哈</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>X能+10×X金</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1138,69 +1138,68 @@
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>花费至多 6 金币，每 1 金币 +2 伤害。
-造成 6 伤害。</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>基础 8 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>可变投入</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>梭哈</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>X能+10×X金</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>花费 10×X 金币。
 造成 27×X 伤害。</t>
         </is>
       </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>金币费降为 8×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>可变投入</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>再加注</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
+        </is>
+      </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>金币费降为 8×X</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
+          <t>12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1212,16 +1211,16 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>再加注</t>
+          <t>全下</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1231,7 +1230,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>X能+7×X金</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1240,221 +1239,221 @@
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>12 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>可变投入</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>全下</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>X能+7×X金</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>花费 7×X 金币。
 对随机敌人造成 9×X 伤害，共 X 次。</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>金币费降为 5×X</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>条件·赌博计数</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>满贯</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>2能+18金</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>花费 18 金币。
 造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>38 / 62</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="15" ht="38" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>打庄</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>2能+15金</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>花费 15 金币。
 对生命值最低的敌人造成 43 伤害。</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>50 伤害</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>翻盘</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
 造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>14 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1">
+          <t>至多 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1462,15 +1461,15 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>真赌</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>摊牌</t>
+          <t>孤注一掷</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1480,27 +1479,28 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+10金</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+          <t>花费 10 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
@@ -1516,16 +1516,16 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>孤注一掷</t>
+          <t>押宝</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1能+10金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1544,69 +1544,68 @@
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>花费 10 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>正面 50 / 反面 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>真赌</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>押宝</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
         </is>
       </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>押牌</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
+        </is>
+      </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>24 / 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1">
+          <t>12 / 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1614,15 +1613,15 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>真赌·自伤/自消耗</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>俄罗斯轮盘</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1637,72 +1636,72 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>加注</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>真赌·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>基础 10 伤害</t>
         </is>
       </c>
     </row>
@@ -1714,20 +1713,20 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗·赌命·血线</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>放血</t>
+          <t>连续下注</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1747,12 +1746,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>造成 9 伤害。自己失去 3 点生命。</t>
+          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>造成 12 伤害</t>
+          <t>额外 +6 伤害</t>
         </is>
       </c>
     </row>
@@ -1764,20 +1763,20 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>连续下注</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1792,17 +1791,17 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>9 / 正面 17</t>
         </is>
       </c>
     </row>
@@ -1818,16 +1817,16 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>买定离手</t>
+          <t>试手气</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1837,7 +1836,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1847,12 +1846,12 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>9 / 正面 17</t>
+          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1868,16 +1867,16 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>试手气</t>
+          <t>双倍下注</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1887,7 +1886,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1897,16 +1896,16 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
+          <t>12 / 正面 12×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1918,11 +1917,11 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>双倍下注</t>
+          <t>翻本</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1937,7 +1936,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1947,12 +1946,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
+          <t>花费 3 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>12 / 正面 12×2</t>
+          <t>13 / 正面 25</t>
         </is>
       </c>
     </row>
@@ -1968,11 +1968,11 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>翻本</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -1996,65 +1996,64 @@
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>13 / 正面 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
         </is>
       </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>5×3 / 正面每次 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>赌博·出千·确定性</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>造成 8 伤害</t>
         </is>
       </c>
     </row>
@@ -2066,20 +2065,20 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>赌博·出千·确定性</t>
+          <t>赌命·血线</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>偷天换日</t>
+          <t>赌命</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2089,22 +2088,23 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+          <t>花费 10 金币。
+造成等于「你已失去生命」的 50% 的伤害。</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>造成 8 伤害</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2116,20 +2116,20 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>赌命·血线</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>赌命</t>
+          <t>底注</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2149,13 +2149,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成等于「你已失去生命」的 50% 的伤害。</t>
+          <t>花费 2 金币。
+造成 11 伤害。</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>造成 14 伤害</t>
         </is>
       </c>
     </row>
@@ -2171,11 +2171,11 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>底注</t>
+          <t>看场</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2200,13 +2200,13 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-造成 10 伤害。</t>
+          <t>花费 3 金币。
+造成 14 伤害，施加 2 易伤。</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>造成 13 伤害</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2251,13 +2251,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-造成 16 伤害，施加 1 易伤。</t>
+          <t>花费 6 金币。
+造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>19 伤害，2 易伤</t>
+          <t>9 点</t>
         </is>
       </c>
     </row>
@@ -2269,20 +2269,20 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>暗注</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2292,78 +2292,77 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>1能+6金</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>花费 6 金币。
-造成 6 点无视格挡的伤害。</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>9 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="38" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>3能+12金</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>花费 12 金币。
 造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>46 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>46 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
+          <t>10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
       <c r="B36" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -2375,16 +2374,16 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>乘胜</t>
+          <t>通杀</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2394,7 +2393,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+5金</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2403,201 +2402,201 @@
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>造成 6 伤害。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>9 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="54" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>通杀</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>20 伤害</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="37" ht="38" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D37" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>晒冷</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>3能+15金</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>花费 15 金币。
 造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>62 伤害</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="38" ht="54" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D38" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>追数</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>2能+8金</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>风头·续风</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>花费 8 金币。
 造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
         </is>
       </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>风头·只读条件</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>叠注</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>36 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
+          <t>10 / 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>叠注</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2607,12 +2606,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+          <t>获得 5 金币。</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>10 / 20</t>
+          <t>获得 7 金币</t>
         </is>
       </c>
     </row>
@@ -2628,16 +2627,16 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>本钱</t>
+          <t>筹码</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2647,7 +2646,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2657,16 +2656,16 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>获得 5 金币。</t>
+          <t>获得 7 金币。</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2678,16 +2677,16 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>筹码</t>
+          <t>派彩</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2697,7 +2696,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+3金</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -2706,68 +2705,68 @@
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>获得 7 金币。</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>获得 9 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>派彩</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>2能+3金</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>获得 22 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>兑筹</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>消耗手牌 1 张，获得 12 金币。</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>获得 22 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
+          <t>获得 16 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
       <c r="B44" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2779,11 +2778,11 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2798,7 +2797,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -2808,12 +2807,12 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
+          <t>获得 18 金币</t>
         </is>
       </c>
     </row>
@@ -2829,16 +2828,16 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>高利贷</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2848,7 +2847,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2858,12 +2857,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>额外抽 1 张</t>
         </is>
       </c>
     </row>
@@ -2879,11 +2878,11 @@
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -2908,12 +2907,12 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
+          <t>每个敌人给予 5 金币。</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
@@ -2929,16 +2928,16 @@
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>抽水</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2958,12 +2957,12 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币。</t>
+          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
@@ -2979,11 +2978,11 @@
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3008,12 +3007,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
@@ -3025,127 +3024,127 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>每张 5 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>引擎产金</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>返水</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="D51" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>利滚利</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>每回合 4 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
           <t>2能</t>
@@ -3158,12 +3157,12 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>每回合 5 金币</t>
+          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
@@ -3175,15 +3174,15 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>自伤/自消耗</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>利滚利</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -3193,7 +3192,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3203,21 +3202,21 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+          <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
+          <t>抽 3 张，18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="38" customHeight="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -3225,20 +3224,20 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗</t>
+          <t>自伤/自消耗·赌命·血线</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>弃牌</t>
+          <t>放血</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3248,22 +3247,22 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+          <t>失去 2 点生命，获得 20 金币。</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>获得 26 金币</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3558,12 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。本回合每花费过 5 金币，额外 +3 格挡。</t>
+          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>每 5 金 +4</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3608,12 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 4 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>6 / 正面 13</t>
+          <t>7 / 正面 13</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3750,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3761,7 +3760,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
+          <t>花费 2 金币。
 获得 15 格挡。</t>
         </is>
       </c>
@@ -3802,7 +3801,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -3812,13 +3811,13 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-获得 5 格挡 3 次。</t>
+          <t>花费 5 金币。
+获得 4 格挡 4 次。</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>7 格挡 3 次</t>
+          <t>6 格挡 4 次</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3862,12 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
+          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>8 格挡</t>
+          <t>9 格挡</t>
         </is>
       </c>
     </row>
@@ -3930,20 +3929,20 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>洗牌</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3953,7 +3952,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3963,12 +3962,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+          <t>消耗 1 张手牌，获得 6 金币。</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -3984,16 +3983,16 @@
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4003,7 +4002,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -4013,12 +4012,12 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>弃置 1 张手牌，抽 2 张牌。</t>
+          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>顶 4 张</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4071,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="38" customHeight="1">
+    <row r="70" ht="22" customHeight="1">
       <c r="B70" s="5" t="inlineStr">
         <is>
           <t>资源</t>
@@ -4080,45 +4079,45 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>回复 2 点生命</t>
         </is>
       </c>
     </row>
@@ -4130,20 +4129,20 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗·赌命·血线</t>
+          <t>真赌</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>血本</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -4153,22 +4152,22 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>失去 5 点生命。获得 2 点能量。</t>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>失去 4 点生命</t>
+          <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4302,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4313,13 +4312,13 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-抽 3 张牌。</t>
+          <t>花费 4 金币。
+抽 2 张牌。</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>抽 4 张牌</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4353,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>0能+6金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4364,13 +4363,13 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>花费 6 金币。
-获得 2 点能量。</t>
+          <t>花费 2 金币。
+获得 1 点能量。</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>获得 3 点</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4865,12 +4864,12 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>获得 1 次必正，抽 1 张牌。</t>
+          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>获得 2 次必正</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5156,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5167,13 +5166,13 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-施加 4 虚弱。</t>
+          <t>花费 3 金币。
+施加 3 虚弱。</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>施加 5 虚弱</t>
+          <t>施加 4 虚弱</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5332,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>6</v>
@@ -5349,19 +5348,21 @@
         <v>1</v>
       </c>
       <c r="J5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="10" t="n"/>
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="10" t="n">
         <v>3</v>
@@ -5370,10 +5371,10 @@
         <v>2</v>
       </c>
       <c r="S5" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -5404,13 +5405,15 @@
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
+      <c r="S6" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="T6" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5477,20 +5480,18 @@
         <v>2</v>
       </c>
       <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P8" s="11" t="n"/>
       <c r="Q8" s="11" t="n">
         <v>3</v>
       </c>
       <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="S8" s="11" t="n"/>
       <c r="T8" s="11" t="n">
         <v>12</v>
       </c>
@@ -5571,7 +5572,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>10</v>
@@ -5589,13 +5590,13 @@
         <v>2</v>
       </c>
       <c r="J11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="L11" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
@@ -5607,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="7" t="n">
         <v>10</v>
@@ -5616,7 +5617,7 @@
         <v>5</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" s="7" t="n">
         <v>87</v>
@@ -5626,7 +5627,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、放血、偷天换日、抽头、割肉、血本），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、偷天换日、放血、抽头、割肉），故机制列合计 92 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
         </is>
       </c>
     </row>
@@ -5822,16 +5823,16 @@
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>花费 2 金币。
-造成 10 伤害。</t>
+造成 11 伤害。</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>造成 13 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
+          <t>造成 14 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>普通</t>
@@ -5862,13 +5863,12 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>花费至多 6 金币，每 1 金币 +2 伤害。
-造成 6 伤害。</t>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>基础 8 伤害</t>
+          <t>基础 10 伤害</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5943,13 +5943,13 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-造成 16 伤害，施加 1 易伤。</t>
+          <t>花费 3 金币。
+造成 14 伤害，施加 2 易伤。</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>19 伤害，2 易伤</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。击杀则获得 10 金币。</t>
+          <t>造成 9 伤害。击杀则获得 15 金币。</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>9 伤害，击杀 +14 金</t>
+          <t>11 伤害，击杀 +19 金</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
+          <t>花费 2 金币。
 获得 15 格挡。</t>
         </is>
       </c>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 4 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>6 / 正面 13</t>
+          <t>7 / 正面 13</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -6145,13 +6145,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-抽 3 张牌。</t>
+          <t>花费 4 金币。
+抽 2 张牌。</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>抽 4 张牌</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -6186,13 +6186,13 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-施加 4 虚弱。</t>
+          <t>花费 3 金币。
+施加 3 虚弱。</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>施加 5 虚弱</t>
+          <t>施加 4 虚弱</t>
         </is>
       </c>
     </row>
@@ -6267,12 +6267,12 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>获得 5 格挡。数值随头顶倍率放大，结算后清空。</t>
+          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>8 格挡</t>
+          <t>9 格挡</t>
         </is>
       </c>
     </row>
@@ -6307,16 +6307,16 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>造成 6 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>9 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
+          <t>10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>普通</t>
@@ -6347,12 +6347,12 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8 金币）。</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>额外抽 1 张</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -6427,13 +6427,13 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-造成 12 伤害；溢出的伤害转为金币。</t>
+          <t>花费 3 金币。
+造成 16 伤害；被格挡抵消的伤害转为金币。</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>16 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。本回合每花费过 5 金币，额外 +3 格挡。</t>
+          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>每 5 金 +4</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>弃置 1 张手牌，抽 2 张牌。</t>
+          <t>消耗 1 张手牌，获得 6 金币。</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -6548,13 +6548,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-获得 5 格挡 3 次。</t>
+          <t>花费 5 金币。
+获得 4 格挡 4 次。</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>7 格挡 3 次</t>
+          <t>6 格挡 4 次</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>0能+6金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -6589,13 +6589,13 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>花费 6 金币。
-获得 2 点能量。</t>
+          <t>花费 2 金币。
+获得 1 点能量。</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>获得 3 点</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>获得 1 次必正，抽 1 张牌。</t>
+          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>获得 2 次必正</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>血本</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>失去 5 点生命。获得 2 点能量。</t>
+          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>失去 4 点生命</t>
+          <t>回复 2 点生命</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>造成 9 伤害。自己失去 3 点生命。</t>
+          <t>失去 2 点生命，获得 20 金币。</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>造成 12 伤害</t>
+          <t>获得 26 金币</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -551,14 +551,14 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4022988505747127</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>赌博 6、风头·兑现 5、击杀产金 4、真赌 4、可变投入 3、特异 3、附加费 3、出千·确定性 2、花费追踪 2、即时产金 1、条件·赌博计数 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
+          <t>赌博 5、风头·兑现 5、击杀产金 4、真赌 4、特异 3、附加费 3、出千·确定性 2、可变投入 2、花费追踪 2、即时产金 1、条件·赌博计数 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.1954022988505747</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>即时产金 10、引擎产金 3、自伤/自消耗 2、赌命·血线 1、赌博 1、风头·兑现 1</t>
+          <t>即时产金 11、引擎产金 3、自伤/自消耗 2、赌博 2、赌命·血线 1、风头·兑现 1</t>
         </is>
       </c>
     </row>
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1264367816091954</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>做局 6、出千·确定性 3、特异 1、赌命·血线 1</t>
+          <t>做局 6、出千·确定性 3、特异 1、赌命·血线 1、附加费 1</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11.4" customWidth="1" min="8" max="8"/>
+    <col width="10.4" customWidth="1" min="8" max="8"/>
     <col width="9.800000000000001" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="30.7" customWidth="1" min="11" max="11"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -935,8 +935,8 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。</t>
+          <t>花费 2 金币。
+对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。每打出一次，伤害永久 +4。</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>X能+10×X金</t>
+          <t>X能+5×X金</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>花费 10×X 金币。
+          <t>花费 5×X 金币。
 造成 27×X 伤害。</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>金币费降为 8×X</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
+          <t>金币费降为 4×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>再加注</t>
+          <t>全下</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>X能+7×X金</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1189,221 +1189,221 @@
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>12 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>可变投入</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>全下</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>X能+7×X金</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>花费 7×X 金币。
 对随机敌人造成 9×X 伤害，共 X 次。</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>金币费降为 5×X</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>条件·赌博计数</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>满贯</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>2能+18金</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>花费 18 金币。
 造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>38 / 62</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>打庄</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>2能+15金</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>花费 15 金币。
 对生命值最低的敌人造成 43 伤害。</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>50 伤害</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>翻盘</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>14 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="38" customHeight="1">
+          <t>至多 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1411,15 +1411,15 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>真赌</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>摊牌</t>
+          <t>孤注一掷</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1429,27 +1429,28 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+10金</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+          <t>花费 10 金币。
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
@@ -1465,16 +1466,16 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>孤注一掷</t>
+          <t>押宝</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1484,7 +1485,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>1能+10金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1493,69 +1494,68 @@
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>花费 10 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>正面 50 / 反面 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>真赌</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>押宝</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
         </is>
       </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>押牌</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24 / 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1">
+          <t>12 / 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>真赌·自伤/自消耗</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>俄罗斯轮盘</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1586,104 +1586,104 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>加注</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>基础 10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>真赌·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>连续下注</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>每次 4 / 正面 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>花费追踪</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>加注</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
           <t>1能</t>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
+          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害。</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>基础 10 伤害</t>
+          <t>额外 2 次</t>
         </is>
       </c>
     </row>
@@ -1713,20 +1713,20 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>连续下注</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>9 / 正面 17</t>
         </is>
       </c>
     </row>
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>买定离手</t>
+          <t>试手气</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>9 / 正面 17</t>
+          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1817,16 +1817,16 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>试手气</t>
+          <t>双倍下注</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1846,16 +1846,16 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
+          <t>12 / 正面 12×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>双倍下注</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1896,16 +1896,17 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
+          <t>花费 3 金币。
+硬币为正时：对随机敌人造成 4 伤害 6 次；硬币为负时：造成 4 伤害 4 次。</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>12 / 正面 12×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
+          <t>5×4 / 正面 5×6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1913,97 +1914,96 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>赌博·出千·确定性</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>翻本</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>赌命·血线</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>13 / 正面 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
+          <t>花费 10 金币。
+造成等于「你已失去生命」的 50% 的伤害。</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2015,15 +2015,15 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>赌博·出千·确定性</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>偷天换日</t>
+          <t>底注</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2038,22 +2038,23 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+          <t>花费 2 金币。
+造成 11 伤害。</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害</t>
+          <t>造成 14 伤害</t>
         </is>
       </c>
     </row>
@@ -2065,20 +2066,20 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>赌命·血线</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>赌命</t>
+          <t>看场</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2088,7 +2089,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2098,13 +2099,13 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成等于「你已失去生命」的 50% 的伤害。</t>
+          <t>花费 3 金币。
+造成 14 伤害，施加 2 易伤。</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -2120,16 +2121,16 @@
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>底注</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2139,7 +2140,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2149,13 +2150,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-造成 11 伤害。</t>
+          <t>花费 6 金币。
+造成 6 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>造成 14 伤害</t>
+          <t>9 点</t>
         </is>
       </c>
     </row>
@@ -2167,20 +2168,20 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2190,129 +2191,128 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-造成 14 伤害，施加 2 易伤。</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>17 伤害，2 易伤</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>花费 6 金币。
-造成 6 点无视格挡的伤害。</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>9 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="38" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>3能+12金</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>花费 12 金币。
 造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>46 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>2能+5金</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>花费 5 金币。
+对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>46 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+          <t>20 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>乘胜</t>
+          <t>晒冷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>3能+15金</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2353,12 +2353,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>花费 15 金币。
+造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>10 伤害</t>
+          <t>62 伤害</t>
         </is>
       </c>
     </row>
@@ -2374,16 +2375,16 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>通杀</t>
+          <t>追数</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2393,23 +2394,23 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>2能+5金</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>风头·续风</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>花费 8 金币。
+造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>20 伤害</t>
+          <t>36 伤害</t>
         </is>
       </c>
     </row>
@@ -2421,20 +2422,20 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·只读条件</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>叠注</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2444,151 +2445,149 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>62 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="54" customHeight="1">
+          <t>12 / 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>风头·续风</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+          <t>获得 5 金币。</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>36 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="38" customHeight="1">
+          <t>获得 7 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>叠注</t>
+          <t>筹码</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>获得 7 金币。</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>派彩</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>10 / 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>本钱</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>起始</t>
-        </is>
-      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>技能</t>
@@ -2596,7 +2595,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>2能+3金</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2606,12 +2605,13 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>获得 5 金币。</t>
+          <t>花费 3 金币。
+获得 18 金币，抽 1 张牌。</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>获得 7 金币</t>
+          <t>获得 22 金币</t>
         </is>
       </c>
     </row>
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>筹码</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币。</t>
+          <t>消耗手牌 1 张，获得 12 金币。</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>获得 16 金币</t>
         </is>
       </c>
     </row>
@@ -2677,11 +2677,11 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>派彩</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -2706,17 +2706,16 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-获得 18 金币，抽 1 张牌。</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>获得 22 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
+          <t>获得 18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2728,128 +2727,128 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>额外抽 1 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>买码</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>每个敌人给予 5 金币。</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>每敌人 7 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>抽水</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>高利贷</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="38" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>散码</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -2857,12 +2856,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
+          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>额外抽 1 张</t>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
@@ -2878,16 +2877,16 @@
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2907,12 +2906,12 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币。</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
@@ -2924,80 +2923,80 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="38" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>至多 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>清码</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3007,12 +3006,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>每回合 5 金币</t>
         </is>
       </c>
     </row>
@@ -3028,168 +3027,168 @@
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>返水</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>自伤/自消耗</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>弃牌</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>抽 3 张，18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>自伤/自消耗·赌命·血线</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>放血</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>每回合开始获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>每回合 4 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>失去 2 点生命，获得 20 金币。</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>获得 26 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>赌博·即时产金</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>翻本</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>利滚利</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>弃牌</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
           <t>技能</t>
@@ -3197,22 +3196,23 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+          <t>花费 10 金币。
+硬币为正时：获得 25 金币；硬币为负时：获得 5 金币。</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>6 / 正面 30</t>
         </is>
       </c>
     </row>
@@ -3224,20 +3224,20 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗·赌命·血线</t>
+          <t>赌博·即时产金</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>放血</t>
+          <t>抽头</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3247,26 +3247,26 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>失去 2 点生命，获得 20 金币。</t>
+          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>获得 26 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="38" customHeight="1">
+          <t>9 / 正面 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
       <c r="B54" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -3274,15 +3274,15 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>赌博·即时产金</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>抽头</t>
+          <t>兑现</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3302,37 +3302,37 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
+          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>产金</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>兑现</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -3378,16 +3378,16 @@
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>保本</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -3406,68 +3406,68 @@
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>12 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>保本</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>花费 10 金币。
 消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>至多 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>自伤/自消耗</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>获得 12 格挡；自己失去 4 点生命。</t>
+        </is>
+      </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>至多 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
+          <t>16 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="38" customHeight="1">
       <c r="B58" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3475,20 +3475,20 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>自伤/自消耗</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>点码</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
+          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -3525,15 +3525,15 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3553,21 +3553,21 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>基础 8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="38" customHeight="1">
+          <t>7 / 正面 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="54" customHeight="1">
       <c r="B60" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3579,16 +3579,16 @@
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -3608,12 +3608,13 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
+          <t>花费 2 金币。
+硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>7 / 正面 13</t>
+          <t>10 / 反面 20</t>
         </is>
       </c>
     </row>
@@ -3629,11 +3630,11 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>反水</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3657,65 +3658,65 @@
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="54" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="38" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>护盘</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+获得 15 格挡。</t>
+        </is>
+      </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
@@ -3731,11 +3732,11 @@
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>护盘</t>
+          <t>护池</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3750,7 +3751,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3759,69 +3760,68 @@
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 15 格挡。</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>护池</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>0能+5金</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 获得 4 格挡 4 次。</t>
         </is>
       </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>6 格挡 4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>6 格挡 4 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
+          <t>9 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="38" customHeight="1">
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3829,95 +3829,95 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·兑现·自伤/自消耗</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>收手</t>
+          <t>割肉</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>9 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="38" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>割肉</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+          <t>消耗 1 张手牌，获得 6 金币。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，获得 6 金币。</t>
+          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>获得 8 金币</t>
+          <t>顶 4 张</t>
         </is>
       </c>
     </row>
@@ -3983,11 +3983,11 @@
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+          <t>消耗 1 张手牌，抽 2 张牌。</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
+          <t>抽 3 张</t>
         </is>
       </c>
     </row>
@@ -4033,178 +4033,178 @@
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>换牌</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>回复 2 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>单双</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>正面 5 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="38" customHeight="1">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>加码</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>分红</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>回复 2 点生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>真赌</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>单双</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>花费追踪</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>流水</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>每 8 金</t>
         </is>
       </c>
     </row>
@@ -4229,20 +4229,20 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>摸牌</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4262,12 +4262,13 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>花费 4 金币。
+抽 2 张牌。</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -4283,11 +4284,11 @@
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>摸牌</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -4302,7 +4303,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>0能+4金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4312,13 +4313,13 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-抽 2 张牌。</t>
+          <t>花费 2 金币。
+获得 1 点能量。</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4330,20 +4331,20 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>割禾青</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4353,23 +4354,22 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>0能+2金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-获得 1 点能量。</t>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>获得 2 点</t>
+          <t>至多 4 张</t>
         </is>
       </c>
     </row>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>至多 4 张</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
@@ -4431,15 +4431,15 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·只读条件</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -4454,59 +4454,59 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>暗记</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>+1 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="38" customHeight="1">
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>风头·只读条件</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>底牌</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
+          <t>你的接下来 2 次赌博必为正面。</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>接下来 3 次必为正面</t>
         </is>
       </c>
     </row>
@@ -4535,11 +4535,11 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>暗记</t>
+          <t>手气正旺</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>你的接下来 2 次赌博必为正面。</t>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>接下来 3 次必为正面</t>
+          <t>+25%</t>
         </is>
       </c>
     </row>
@@ -4585,16 +4585,16 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>手气正旺</t>
+          <t>赌神</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+          <t>你的所有赌博视为正面。</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>费用变为 2</t>
         </is>
       </c>
     </row>
@@ -4635,26 +4635,26 @@
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>赌神</t>
+          <t>叠码</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>3能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>你的所有赌博视为正面。</t>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>费用变为 2</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
@@ -4685,16 +4685,16 @@
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>出千</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4735,11 +4735,11 @@
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
+          <t>你的风头倍率翻倍（不清空）。</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>做局</t>
+          <t>出千·确定性</t>
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>倍投</t>
+          <t>封口</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
+          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -4835,76 +4835,76 @@
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>千王</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="38" customHeight="1">
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>获得 2 次必正，抽 2 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>千王</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -4913,64 +4913,64 @@
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="38" customHeight="1">
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>瞒天过海</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
 本回合你接下来的 3 次赌博必为正面。</t>
         </is>
       </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
+        </is>
+      </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>4 次</t>
+          <t>本场战斗前 2 次</t>
         </is>
       </c>
     </row>
@@ -4982,15 +4982,15 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>赌命·血线</t>
         </is>
       </c>
       <c r="D88" s="11" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -5000,62 +5000,62 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="38" customHeight="1">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>再加注</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>赌命·血线</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>押注</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+3金</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -5065,12 +5065,13 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+          <t>花费 3 金币。
+获得 5 点活力（下次攻击额外造成等量伤害）。</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>8 点</t>
         </is>
       </c>
     </row>
@@ -5332,10 +5333,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n">
@@ -5374,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -5386,7 +5387,7 @@
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="11" t="n"/>
       <c r="G6" s="11" t="n"/>
@@ -5397,7 +5398,7 @@
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>3</v>
@@ -5413,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5502,7 +5503,9 @@
           <t>操控·辅助</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -5528,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -5569,10 +5572,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>10</v>
@@ -5596,7 +5599,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
@@ -5627,7 +5630,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、偷天换日、放血、抽头、割肉），故机制列合计 92 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、偷天换日、放血、翻本、抽头、割肉），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5657,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="11.4" customWidth="1" min="6" max="6"/>
+    <col width="10.4" customWidth="1" min="6" max="6"/>
     <col width="9.800000000000001" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="30.7" customWidth="1" min="9" max="9"/>
@@ -6780,7 +6783,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>X能+10×X金</t>
+          <t>X能+5×X金</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -6790,13 +6793,13 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>花费 10×X 金币。
+          <t>花费 5×X 金币。
 造成 27×X 伤害。</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>金币费降为 8×X</t>
+          <t>金币费降为 4×X</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6834,12 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害。</t>
+          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害。</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>额外 2 次</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6864,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -6871,8 +6874,8 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。</t>
+          <t>花费 2 金币。
+对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币。每打出一次，伤害永久 +4。</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -6902,7 +6905,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -6952,12 +6955,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>10 / 20</t>
+          <t>12 / 24</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6980,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -6992,13 +6995,13 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 10 伤害。</t>
+          <t>花费 10 金币。
+硬币为正时：获得 25 金币；硬币为负时：获得 5 金币。</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>13 / 正面 25</t>
+          <t>6 / 正面 30</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7026,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -7033,13 +7036,13 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 3 次；硬币为负时：对随机敌人造成 4 伤害 3 次。</t>
+          <t>花费 3 金币。
+硬币为正时：对随机敌人造成 4 伤害 6 次；硬币为负时：造成 4 伤害 4 次。</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>5×4 / 正面 5×6</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7609,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="54" customHeight="1">
+    <row r="52" ht="38" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7622,12 +7625,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+3金</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -7637,12 +7640,13 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>自动花费至多 9 金币，按投入解锁：造成 8 伤害；≥3 金再施加 2 易伤；≥6 金再抽 1 张；≥9 金再 +8 伤害。</t>
+          <t>花费 3 金币。
+获得 5 点活力（下次攻击额外造成等量伤害）。</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>12 伤害</t>
+          <t>8 点</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1954022988505747</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>即时产金 11、引擎产金 3、自伤/自消耗 2、赌博 2、赌命·血线 1、风头·兑现 1</t>
+          <t>即时产金 10、引擎产金 3、自伤/自消耗 2、赌博 2、赌命·血线 1、风头·兑现 1</t>
         </is>
       </c>
     </row>
@@ -605,14 +605,14 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1264367816091954</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>特异 3、花费追踪 2、附加费 2、风头·兑现 2、即时产金 1、真赌 1、风头·只读条件 1</t>
+          <t>特异 2、花费追踪 2、附加费 2、风头·兑现 2、即时产金 1、真赌 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1609195402298851</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>做局 6、出千·确定性 3、特异 1、赌命·血线 1、附加费 1</t>
+          <t>做局 6、出千·确定性 4、附加费 2、特异 1、赌命·血线 1</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>消耗你所有的必正次数，每消耗 1 次造成 9 伤害（没有必正时无事发生）。</t>
+          <t>你的每 1 次必正造成 9 伤害（不消耗必正；没有必正时无事发生）。</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="38" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1343,13 +1343,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
+          <t>造成 6 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>14 / 30</t>
+          <t>8 / 18</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1495,12 @@
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>24 / 正面 36 / 反面失 4</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2150,12 @@
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
-造成 6 点无视格挡的伤害。</t>
+造成 13 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>16 点</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2594,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2605,8 +2604,8 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-获得 18 金币，抽 1 张牌。</t>
+          <t>花费 5 金币。
+获得 18 金币，抽 2 张牌。</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2627,11 +2626,11 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2646,7 +2645,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2656,16 +2655,16 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
+          <t>每张手牌获得 2 金币。</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
+          <t>每张 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2691,7 +2690,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2706,12 +2705,12 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
+          <t>获得 50 金币。每回合开始失去 5 金币。</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>获得 60 金币</t>
         </is>
       </c>
     </row>
@@ -2827,11 +2826,11 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2856,12 +2855,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
@@ -2873,127 +2872,127 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>每回合开始获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>每张 5 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>引擎产金</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>返水</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="D48" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>利滚利</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>每回合开始获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>每回合 4 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>2能</t>
@@ -3006,12 +3005,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>每回合 5 金币</t>
+          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
@@ -3023,15 +3022,15 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>自伤/自消耗</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>利滚利</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -3041,7 +3040,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -3051,21 +3050,21 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+          <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
+          <t>抽 3 张，18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1">
       <c r="B50" s="5" t="inlineStr">
         <is>
           <t>产金</t>
@@ -3073,20 +3072,20 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>自伤/自消耗</t>
+          <t>自伤/自消耗·赌命·血线</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>弃牌</t>
+          <t>放血</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3096,26 +3095,26 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+          <t>失去 2 点生命，获得 20 金币。</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="38" customHeight="1">
+          <t>获得 26 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -3123,20 +3122,20 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗·赌命·血线</t>
+          <t>赌博·即时产金</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>放血</t>
+          <t>翻本</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3146,77 +3145,77 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>失去 2 点生命，获得 20 金币。</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>获得 26 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="54" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>赌博·即时产金</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>翻本</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>0能+10金</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 硬币为正时：获得 25 金币；硬币为负时：获得 5 金币。</t>
         </is>
       </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>6 / 正面 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>赌博·即时产金</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>抽头</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 20 金币；硬币为负时：获得 10 金币。</t>
+        </is>
+      </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>6 / 正面 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="38" customHeight="1">
+          <t>12 / 正面 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -3224,15 +3223,15 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>赌博·即时产金</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>抽头</t>
+          <t>兑现</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3252,37 +3251,37 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
+          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="38" customHeight="1">
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>产金</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>兑现</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3302,17 +3301,17 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -3328,16 +3327,16 @@
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>保本</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3347,7 +3346,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3356,68 +3355,68 @@
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>12 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>保本</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>至多 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>自伤/自消耗</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>获得 12 格挡；自己失去 4 点生命。</t>
+        </is>
+      </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>至多 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
+          <t>16 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="38" customHeight="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3425,20 +3424,20 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>自伤/自消耗</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>点码</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3448,7 +3447,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3458,12 +3457,12 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
+          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -3475,15 +3474,15 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -3503,21 +3502,21 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>基础 8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="38" customHeight="1">
+          <t>7 / 正面 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="54" customHeight="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3529,16 +3528,16 @@
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3548,7 +3547,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3558,12 +3557,13 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
+          <t>花费 3 金币。
+硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 10 格挡。</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>7 / 正面 13</t>
+          <t>12 / 正面 19</t>
         </is>
       </c>
     </row>
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>反水</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3607,65 +3607,65 @@
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="54" customHeight="1">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>花费 2 金币。
 硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="38" customHeight="1">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>护盘</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+获得 15 格挡。</t>
+        </is>
+      </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
@@ -3681,11 +3681,11 @@
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>护盘</t>
+          <t>护池</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -3709,69 +3709,68 @@
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 15 格挡。</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>获得 18 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>护池</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>0能+5金</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>花费 5 金币。
 获得 4 格挡 4 次。</t>
         </is>
       </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>6 格挡 4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>6 格挡 4 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
+          <t>9 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="38" customHeight="1">
       <c r="B64" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3779,95 +3778,95 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·兑现·自伤/自消耗</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>收手</t>
+          <t>割肉</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>9 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="38" customHeight="1">
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>割肉</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+          <t>消耗 1 张手牌，获得 6 金币。</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -3879,20 +3878,20 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -3912,12 +3911,12 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，获得 6 金币。</t>
+          <t>消耗 1 张手牌，抽 2 张牌。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>获得 8 金币</t>
+          <t>抽 3 张</t>
         </is>
       </c>
     </row>
@@ -3933,73 +3932,73 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>回复 2 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="38" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>单双</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>换牌</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
           <t>1能</t>
@@ -4007,17 +4006,17 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博·真赌</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
@@ -4029,20 +4028,20 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>分红</t>
+          <t>流水</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4052,7 +4051,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4062,12 +4061,12 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
+          <t>你每累计花费 10 金币，抽 1 张牌。</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>回复 2 点生命</t>
+          <t>每累计 8 金币</t>
         </is>
       </c>
     </row>
@@ -4079,20 +4078,20 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4107,21 +4106,21 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
+          <t>每 8 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="38" customHeight="1">
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>资源</t>
@@ -4129,30 +4128,30 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>摸牌</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4162,12 +4161,13 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+          <t>花费 4 金币。
+抽 2 张牌。</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -4179,20 +4179,20 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4212,12 +4212,13 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>花费 2 金币。
+获得 1 点能量。</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4229,20 +4230,20 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>摸牌</t>
+          <t>割禾青</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4252,23 +4253,22 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>0能+4金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-抽 2 张牌。</t>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>至多 4 张</t>
         </is>
       </c>
     </row>
@@ -4280,20 +4280,20 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4303,23 +4303,22 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>0能+2金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-获得 1 点能量。</t>
+          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>获得 2 点</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
@@ -4331,20 +4330,20 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·只读条件</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4354,47 +4353,47 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>至多 4 张</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
     <row r="76" ht="38" customHeight="1">
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>操控·辅助</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>做局</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>暗记</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4404,52 +4403,53 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
+          <t>花费 2 金币。
+你的接下来 2 次赌博必为正面。</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>+1 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="38" customHeight="1">
+          <t>接下来 3 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>操控·辅助</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>做局</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>底牌</t>
+          <t>手气正旺</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>+25%</t>
         </is>
       </c>
     </row>
@@ -4485,26 +4485,26 @@
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>暗记</t>
+          <t>赌神</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>你的接下来 2 次赌博必为正面。</t>
+          <t>你的所有赌博视为正面。</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>接下来 3 次必为正面</t>
+          <t>费用变为 2</t>
         </is>
       </c>
     </row>
@@ -4535,11 +4535,11 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>手气正旺</t>
+          <t>叠码</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
@@ -4585,11 +4585,11 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>赌神</t>
+          <t>出千</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>3能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>你的所有赌博视为正面。</t>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>费用变为 2</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4635,16 +4635,16 @@
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+          <t>你的风头倍率翻倍（不清空）。</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
@@ -4681,20 +4681,20 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>做局</t>
+          <t>出千·确定性</t>
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>抽水</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
+          <t>获得 2 次必正，以及 5 点活力。</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>3 次必正</t>
         </is>
       </c>
     </row>
@@ -4731,20 +4731,20 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>做局</t>
+          <t>出千·确定性</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>倍投</t>
+          <t>封口</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
+          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -4785,76 +4785,76 @@
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>千王</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="38" customHeight="1">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>获得 2 次必正，抽 2 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>千王</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4863,64 +4863,64 @@
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="38" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>瞒天过海</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>花费 6 金币。
 本回合你接下来的 3 次赌博必为正面。</t>
         </is>
       </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
+        </is>
+      </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>4 次</t>
+          <t>本场战斗前 2 次</t>
         </is>
       </c>
     </row>
@@ -4932,15 +4932,15 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>赌命·血线</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4950,62 +4950,62 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="38" customHeight="1">
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>兑筹</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>赌命·血线</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="n">
-        <v>86</v>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>押注</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -5015,12 +5015,13 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>你造成的伤害获得「已失去生命」的 10% 加成。</t>
+          <t>花费 6 金币。
+获得 2 点力量。</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>获得 3 点力量</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5399,7 @@
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>3</v>
@@ -5414,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5489,12 +5490,12 @@
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="11" t="n"/>
       <c r="T8" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -5504,7 +5505,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
@@ -5525,13 +5526,13 @@
         <v>1</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -5572,7 +5573,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>2</v>
@@ -5599,7 +5600,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
@@ -5614,10 +5615,10 @@
         <v>5</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S11" s="7" t="n">
         <v>3</v>
@@ -7046,7 +7047,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
+    <row r="38" ht="38" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7067,7 +7068,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -7077,7 +7078,8 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>你的接下来 2 次赌博必为正面。</t>
+          <t>花费 2 金币。
+你的接下来 2 次赌博必为正面。</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -7107,7 +7109,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -7117,8 +7119,8 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-获得 18 金币，抽 1 张牌。</t>
+          <t>花费 5 金币。
+获得 18 金币，抽 2 张牌。</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -7158,16 +7160,16 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，将其中 1 张置入弃牌堆。</t>
+          <t>每张手牌获得 2 金币。</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
+          <t>每张 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
       <c r="B41" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7188,7 +7190,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -7198,12 +7200,13 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币。</t>
+          <t>花费 6 金币。
+获得 2 点力量。</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
+          <t>获得 3 点力量</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7241,12 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 14 金币；硬币为负时：获得 7 金币。</t>
+          <t>硬币为正时：获得 20 金币；硬币为负时：获得 10 金币。</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
+          <t>12 / 正面 24</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7271,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -7278,13 +7281,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-硬币为正时：获得 8 格挡；硬币为负时：获得 !TailsBlock! 格挡。</t>
+          <t>花费 3 金币。
+硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 10 格挡。</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>10 / 反面 20</t>
+          <t>12 / 正面 19</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7331,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1">
+    <row r="45" ht="22" customHeight="1">
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7344,7 +7347,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7359,12 +7362,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）。</t>
+          <t>获得 50 金币。每回合开始失去 5 金币。</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>获得 60 金币</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7684,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8 金币）。</t>
+          <t>获得 2 次必正，以及 5 点活力。</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>3 次必正</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7725,12 @@
       <c r="H54" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 6 点生命。</t>
+硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>24 / 正面 36 / 反面失 4</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7935,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="54" customHeight="1">
+    <row r="60" ht="38" customHeight="1">
       <c r="B60" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7953,7 +7956,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -7963,13 +7966,12 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-造成 10 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
+          <t>造成 6 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>14 / 30</t>
+          <t>8 / 18</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8007,12 @@
       <c r="H61" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
-造成 6 点无视格挡的伤害。</t>
+造成 13 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>16 点</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8127,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>消耗你所有的必正次数，每消耗 1 次造成 9 伤害（没有必正时无事发生）。</t>
+          <t>你的每 1 次必正造成 9 伤害（不消耗必正；没有必正时无事发生）。</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.1954022988505747</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>即时产金 10、引擎产金 3、自伤/自消耗 2、赌博 2、赌命·血线 1、风头·兑现 1</t>
+          <t>即时产金 11、引擎产金 3、自伤/自消耗 2、赌博 2、赌命·血线 1、风头·兑现 1</t>
         </is>
       </c>
     </row>
@@ -587,14 +587,14 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1264367816091954</v>
+        <v>0.1149425287356322</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>赌博 3、特异 2、自伤/自消耗 2、附加费 2、风头·兑现 2、花费追踪 1</t>
+          <t>赌博 3、特异 2、附加费 2、风头·兑现 2、花费追踪 1、自伤/自消耗 1</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>特异 2、花费追踪 2、附加费 2、风头·兑现 2、即时产金 1、真赌 1、风头·只读条件 1</t>
+          <t>特异 3、附加费 2、风头·兑现 2、即时产金 1、真赌 1、花费追踪 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -2826,11 +2826,11 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+          <t>每张已消耗的牌，获得 2 金币。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>每张 3 金</t>
         </is>
       </c>
     </row>
@@ -2872,145 +2872,145 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>清码</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>消耗全部手牌，每张获得 7 金币。</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>每张 9 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
           <t>引擎产金</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D47" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>返水</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>每回合开始获得 3 金币。</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>每回合 4 金币</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="38" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="48" ht="38" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>引擎产金</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D48" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>台规</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>每回合 5 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>利滚利</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
@@ -3022,397 +3022,397 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
+          <t>引擎产金</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>利滚利</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
           <t>自伤/自消耗</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D50" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>弃牌</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>消耗</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>消耗。抽 2 张牌，获得 14 金币。</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>抽 3 张，18 金币</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
+    <row r="51" ht="38" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>自伤/自消耗·赌命·血线</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D51" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>放血</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>失去 2 点生命，获得 20 金币。</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>获得 26 金币</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="54" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52" ht="54" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>赌博·即时产金</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D52" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>翻本</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0能+10金</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 硬币为正时：获得 25 金币；硬币为负时：获得 5 金币。</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>6 / 正面 30</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53" ht="38" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>赌博·即时产金</t>
         </is>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D53" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>抽头</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>硬币为正时：获得 20 金币；硬币为负时：获得 10 金币。</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>12 / 正面 24</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>产金</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>风头·兑现</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D54" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>兑现</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>获得 9 金币</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="38" customHeight="1">
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>保底</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="D55" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>将 1 张手牌放回抽牌堆，获得 9 格挡。</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>12 格挡</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="38" customHeight="1">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="56" ht="38" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D56" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>保本</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>2能+10金</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 消耗你一半金币，获得等量格挡（至多 30）。</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>至多 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>16 格挡</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="54" customHeight="1">
+    <row r="60" ht="70" customHeight="1">
       <c r="B60" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -3608,13 +3608,13 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
+          <t>花费 3 金币。
+硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>12+12 / 7+7</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
+    <row r="66" ht="38" customHeight="1">
       <c r="B66" s="5" t="inlineStr">
         <is>
           <t>资源</t>
@@ -3882,11 +3882,11 @@
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>换牌</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>获得 1 点能量。每拥有 50 金币，额外 +1 点能量。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>基础 2 能量</t>
         </is>
       </c>
     </row>
@@ -3932,178 +3932,178 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>换牌</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>将任意张手牌放回抽牌堆，再抽等量的牌。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>分红</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>0能</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>每回合开始支付 3 金币，回复 1 点生命。</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>回复 2 点生命</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="38" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+    <row r="69" ht="38" customHeight="1">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>真赌</t>
         </is>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D69" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>单双</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>赌博·真赌</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="K69" s="3" t="inlineStr">
         <is>
           <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>花费追踪</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n">
+      <c r="D70" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>流水</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>每累计 8 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="38" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>花费追踪</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>加码</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>你每累计花费 6 金币，抽 1 张牌。</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>每累计 5 金币</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>3</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5446,7 +5446,7 @@
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="10" t="n">
         <v>2</v>
@@ -5454,7 +5454,7 @@
       <c r="R7" s="10" t="n"/>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5479,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="n">
@@ -5490,7 +5490,7 @@
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="11" t="n"/>
@@ -5594,13 +5594,13 @@
         <v>2</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
@@ -5612,10 +5612,10 @@
         <v>1</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R11" s="7" t="n">
         <v>6</v>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌。</t>
+          <t>你每累计花费 6 金币，抽 1 张牌。</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>每累计 5 金币</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="54" customHeight="1">
+    <row r="55" ht="70" customHeight="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -7765,13 +7765,13 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 5 格挡。</t>
+          <t>花费 3 金币。
+硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>12+12 / 7+7</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="38" customHeight="1">
+    <row r="57" ht="22" customHeight="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡。每张已消耗的牌额外 +2 格挡（至多 +10）。</t>
+          <t>每张已消耗的牌，获得 2 金币。</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>12 格挡</t>
+          <t>每张 3 金</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点能量。本回合每花费过 10 金币，额外 +1（至多 3 点）。</t>
+          <t>获得 1 点能量。每拥有 50 金币，额外 +1 点能量。</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>基础 2 能量</t>
         </is>
       </c>
     </row>
@@ -7926,12 +7926,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币。</t>
+          <t>消耗全部手牌，每张获得 7 金币。</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>每张 9 金</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命。</t>
+          <t>将 1 张手牌放回抽牌堆，获得 9 格挡。</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8087,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌。</t>
+          <t>将任意张手牌放回抽牌堆，再抽等量的牌。</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -551,14 +551,14 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.3448275862068966</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>赌博 5、风头·兑现 5、击杀产金 4、真赌 4、特异 3、附加费 3、出千·确定性 2、可变投入 2、花费追踪 2、即时产金 1、条件·赌博计数 1、自伤/自消耗 1、赌命·血线 1、风头·只读条件 1</t>
+          <t>赌博 5、特异 4、风头·兑现 4、击杀产金 3、附加费 3、出千·确定性 2、可变投入 2、真赌 2、花费追踪 2、即时产金 1、条件·赌博计数 1、赌命·血线 1、风头·只读条件 1</t>
         </is>
       </c>
     </row>
@@ -580,21 +580,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1149425287356322</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>赌博 3、特异 2、附加费 2、风头·兑现 2、花费追踪 1、自伤/自消耗 1</t>
+          <t>特异 4、赌博 3、花费追踪 2、附加费 2、风头·兑现 2、击杀产金 1</t>
         </is>
       </c>
     </row>
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1609195402298851</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>做局 6、出千·确定性 4、附加费 2、特异 1、赌命·血线 1</t>
+          <t>做局 6、出千·确定性 4、特异 2、附加费 2、赌命·血线 1</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 35 伤害。击杀则获得 25 金币。</t>
+          <t>花费 10 金币。
+造成 40 伤害。击杀则获得 30 金币。</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>40 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
+          <t>46 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1004,20 +1004,20 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>击杀产金</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>截胡</t>
+          <t>吃水</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1037,13 +1037,13 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
+          <t>花费 3 金币。
+造成 16 伤害；被格挡抵消的伤害转为金币。</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -1055,20 +1055,20 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>可变投入</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>梭哈</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>X能+5×X金</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1088,13 +1088,13 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-造成 16 伤害；被格挡抵消的伤害转为金币。</t>
+          <t>花费 5×X 金币。
+造成 27×X 伤害。</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>20 伤害</t>
+          <t>金币费降为 4×X</t>
         </is>
       </c>
     </row>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>梭哈</t>
+          <t>全下</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>X能+5×X金</t>
+          <t>X能+7×X金</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>花费 5×X 金币。
-造成 27×X 伤害。</t>
+          <t>花费 7×X 金币。
+对随机敌人造成 12×X 伤害，共 X 次。</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>金币费降为 4×X</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
+          <t>金币费降为 5×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1157,15 +1157,15 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>可变投入</t>
+          <t>条件·赌博计数</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>全下</t>
+          <t>满贯</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>X能+7×X金</t>
+          <t>1能+9金</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>花费 7×X 金币。
-对随机敌人造成 9×X 伤害，共 X 次。</t>
+          <t>花费 9 金币。
+造成 36 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>金币费降为 5×X</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
+          <t>44 / 72</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1208,15 +1208,15 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>条件·赌博计数</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>满贯</t>
+          <t>俄罗斯轮盘</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2能+18金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1241,13 +1241,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>花费 18 金币。
-造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
+          <t>每回合开始随机开一枪：自己受到 3 点伤害并获得 5 金币，或对随机敌人造成 10 点伤害。</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>38 / 62</t>
+          <t>自己 2 伤+7 金 / 敌人 14 伤</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1281,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1292,13 +1291,12 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-对生命值最低的敌人造成 43 伤害。</t>
+          <t>对生命值最低的敌人造成 15 伤害。若你的金币少于 100，伤害翻倍。</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>50 伤害</t>
+          <t>19 / 翻倍 38</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1381,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1393,12 +1391,12 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 30）。</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1447,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
+          <t>正面 55 / 反面 32</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1502,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1512,20 +1510,20 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>真赌</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>加注</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1540,21 +1538,21 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
+          <t>基础 10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1562,20 +1560,20 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>真赌·自伤/自消耗</t>
+          <t>花费追踪</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>俄罗斯轮盘</t>
+          <t>连续下注</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1585,26 +1583,26 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害。</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
+          <t>额外 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1612,15 +1610,15 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>加注</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1640,17 +1638,17 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1。</t>
+          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>基础 10 伤害</t>
+          <t>9 / 正面 17</t>
         </is>
       </c>
     </row>
@@ -1662,20 +1660,20 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>连续下注</t>
+          <t>试手气</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1690,17 +1688,17 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害。</t>
+          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>额外 2 次</t>
+          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1716,16 +1714,16 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>买定离手</t>
+          <t>双倍下注</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1745,16 +1743,16 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>9 / 正面 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="38" customHeight="1">
+          <t>12 / 正面 12×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
@@ -1766,16 +1764,16 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>试手气</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1785,7 +1783,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -1795,12 +1793,13 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>花费 3 金币。
+硬币为正时：对随机敌人造成 4 伤害 6 次；硬币为负时：造成 4 伤害 4 次。</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>造成 7 伤害。正面 → 改为 14 伤害</t>
+          <t>5×4 / 正面 5×6</t>
         </is>
       </c>
     </row>
@@ -1812,96 +1811,96 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
+          <t>赌博·出千·确定性</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>双倍下注</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>赌命·血线</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>硬币为正时：造成 10 伤害两次；硬币为负时：造成 10 伤害。</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>12 / 正面 12×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>花费 3 金币。
-硬币为正时：对随机敌人造成 4 伤害 6 次；硬币为负时：造成 4 伤害 4 次。</t>
+          <t>花费 10 金币。
+造成等于「你已失去生命」的 50% 的伤害。</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>5×4 / 正面 5×6</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -1913,15 +1912,15 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>赌博·出千·确定性</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>偷天换日</t>
+          <t>底注</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1936,22 +1935,23 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 5 伤害，并获得 1 次必正；硬币为负时：造成 5 伤害。</t>
+          <t>花费 2 金币。
+造成 11 伤害。</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害</t>
+          <t>造成 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1963,20 +1963,20 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>赌命·血线</t>
+          <t>附加费</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>赌命</t>
+          <t>看场</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -1996,13 +1996,13 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-造成等于「你已失去生命」的 50% 的伤害。</t>
+          <t>花费 3 金币。
+造成 14 伤害，施加 2 易伤。</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -2018,16 +2018,16 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>底注</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2047,13 +2047,13 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-造成 11 伤害。</t>
+          <t>花费 6 金币。
+造成 13 点无视格挡的伤害。</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>造成 14 伤害</t>
+          <t>16 点</t>
         </is>
       </c>
     </row>
@@ -2065,132 +2065,131 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>3能+10金</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>花费 10 金币。
+造成 48 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>54 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>花费 3 金币。
-造成 14 伤害，施加 2 易伤。</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>17 伤害，2 易伤</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>10 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>花费 6 金币。
-造成 13 点无视格挡的伤害。</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>16 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>2能+5金</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2199,237 +2198,234 @@
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>花费 12 金币。
-造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>46 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>乘胜</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>造成 7 伤害。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>10 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>通杀</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 对所有敌人造成 16 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>20 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>追数</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>风头·续风</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>造成 20 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>24 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>风头·只读条件</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>叠注</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+        </is>
+      </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>20 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="38" customHeight="1">
+          <t>12 / 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>起始</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>获得 5 金币。</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>62 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1">
+          <t>获得 7 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>筹码</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>风头·续风</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+          <t>获得 7 金币。</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>获得 9 金币</t>
         </is>
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>产金</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>即时产金</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>叠注</t>
+          <t>派彩</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2439,12 +2435,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2454,12 +2450,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+          <t>花费 5 金币。
+获得 18 金币，抽 2 张牌。</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>12 / 24</t>
+          <t>获得 22 金币</t>
         </is>
       </c>
     </row>
@@ -2475,16 +2472,16 @@
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>本钱</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>起始</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2504,12 +2501,12 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>获得 5 金币。</t>
+          <t>每张手牌获得 2 金币。</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>获得 7 金币</t>
+          <t>每张 3 金币</t>
         </is>
       </c>
     </row>
@@ -2525,26 +2522,26 @@
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>筹码</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2554,12 +2551,12 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>获得 7 金币。</t>
+          <t>获得 50 金币。每回合开始失去 5 金币。</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>获得 9 金币</t>
+          <t>获得 60 金币</t>
         </is>
       </c>
     </row>
@@ -2575,16 +2572,16 @@
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>派彩</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2594,7 +2591,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2604,13 +2601,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>花费 5 金币。
-获得 18 金币，抽 2 张牌。</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>获得 22 金币</t>
+          <t>额外抽 1 张</t>
         </is>
       </c>
     </row>
@@ -2626,16 +2622,16 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>数牌</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2645,7 +2641,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2655,12 +2651,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>每张手牌获得 2 金币。</t>
+          <t>每个敌人给予 5 金币。</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>每张 3 金币</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
@@ -2676,11 +2672,11 @@
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>高利贷</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2690,12 +2686,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -2705,16 +2701,16 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>获得 50 金币。每回合开始失去 5 金币。</t>
+          <t>每张已消耗的牌，获得 2 金币。</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>获得 60 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
+          <t>每张 3 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2726,16 +2722,16 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2755,12 +2751,12 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币。（升级：额外抽 1 张）</t>
+          <t>消耗全部手牌，每张获得 7 金币。</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>额外抽 1 张</t>
+          <t>每张 9 金</t>
         </is>
       </c>
     </row>
@@ -2772,15 +2768,15 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2790,7 +2786,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2805,16 +2801,16 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币。</t>
+          <t>每回合开始获得 3 金币。</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
+          <t>每回合 4 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>产金</t>
@@ -2822,15 +2818,15 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>台规</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2840,12 +2836,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2855,12 +2851,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>每张已消耗的牌，获得 2 金币。</t>
+          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>每张 3 金</t>
+          <t>每回合 5 金币</t>
         </is>
       </c>
     </row>
@@ -2872,30 +2868,30 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>即时产金</t>
+          <t>引擎产金</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -2905,12 +2901,12 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>消耗全部手牌，每张获得 7 金币。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 3 金币。</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>每张 9 金</t>
+          <t>额外 5 金币</t>
         </is>
       </c>
     </row>
@@ -2922,25 +2918,25 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>自伤/自消耗</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>返水</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2950,17 +2946,17 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>每回合开始获得 3 金币。</t>
+          <t>消耗。抽 2 张牌，获得 16 金币。</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>每回合 4 金币</t>
+          <t>抽 3 张，20 金币</t>
         </is>
       </c>
     </row>
@@ -2972,316 +2968,317 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>引擎产金</t>
+          <t>自伤/自消耗·赌命·血线</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>放血</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>失去 2 点生命，获得 20 金币。</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>获得 26 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>赌博·即时产金</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>翻本</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币。每次掷出正面，额外获得 3 金币。</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>引擎产金</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>利滚利</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>弃牌</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>抽 3 张，18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>自伤/自消耗·赌命·血线</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>放血</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>失去 2 点生命，获得 20 金币。</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>获得 26 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="54" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>产金</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>赌博·即时产金</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>翻本</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>0能+10金</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
 硬币为正时：获得 25 金币；硬币为负时：获得 5 金币。</t>
         </is>
       </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>6 / 正面 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>赌博·即时产金</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>抽头</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>赌博</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>硬币为正时：获得 20 金币；硬币为负时：获得 10 金币。</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>12 / 正面 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>兑现</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>击杀产金·特异</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>截胡</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>花费 6 金币。
+获得 16 格挡，并获得等量金币。</t>
+        </is>
+      </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>6 / 正面 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="38" customHeight="1">
+          <t>20 格挡 / 20 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>产金</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>赌博·即时产金</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>抽头</t>
+          <t>晒冷</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>赌博</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 20 金币；硬币为负时：获得 10 金币。</t>
+          <t>本场战斗中，你每次获得金币时，获得等量格挡。</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>12 / 正面 24</t>
+          <t>等量 +5 格挡</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>产金</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>特异</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>兑现</t>
+          <t>抵押</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3296,84 +3293,84 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>将 1 张手牌放回抽牌堆，获得 9 格挡。</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>12 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>点码</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>获得 9 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>基础 8 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>将 1 张手牌放回抽牌堆，获得 9 格挡。</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>12 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>特异</t>
+          <t>花费追踪·特异</t>
         </is>
       </c>
       <c r="D56" s="11" t="n">
@@ -3391,12 +3388,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -3406,13 +3403,12 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-消耗你一半金币，获得等量格挡（至多 30）。</t>
+          <t>本场战斗中，你每花费 1 金币，获得 1 点敏捷。</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>每金 +1 力量 +1 敏捷</t>
         </is>
       </c>
     </row>
@@ -3424,15 +3420,15 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>花费追踪</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3452,21 +3448,21 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赌博</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡。本回合每花费 1 金币，额外 +1 格挡。</t>
+          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>基础 8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="38" customHeight="1">
+          <t>7 / 正面 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="54" customHeight="1">
       <c r="B58" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3478,16 +3474,16 @@
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3497,7 +3493,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -3506,115 +3502,116 @@
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>7 / 正面 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="54" customHeight="1">
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>赌博</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 10 格挡。</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>12 / 正面 19</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="70" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
+    <row r="59" ht="70" customHeight="1">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D59" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>反水</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>1能+3金</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>赌博</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
 硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
         </is>
       </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>12+12 / 7+7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="38" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>护盘</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>花费 2 金币。
+获得 15 格挡。</t>
+        </is>
+      </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>12+12 / 7+7</t>
+          <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
@@ -3630,11 +3627,11 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>护盘</t>
+          <t>护池</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3649,7 +3646,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3658,65 +3655,64 @@
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>花费 2 金币。
-获得 15 格挡。</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>附加费</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>护池</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>0能+5金</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
 获得 4 格挡 4 次。</t>
         </is>
       </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>6 格挡 4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>风头·兑现</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>6 格挡 4 次</t>
+          <t>9 格挡</t>
         </is>
       </c>
     </row>
@@ -3732,178 +3728,178 @@
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>收手</t>
+          <t>割肉</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>获得 12 格挡。数值随头顶倍率放大，结算后清空。</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>15 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>即时产金</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>获得 6 格挡。数值随头顶倍率放大，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>9 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>风头·兑现·自伤/自消耗</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>割肉</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，获得 6 金币。</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>获得 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="38" customHeight="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>加码</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>13 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="B65" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>获得 1 点能量。每拥有 50 金币，额外 +1 点能量。</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>基础 2 能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>资源</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>即时产金</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>洗牌</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>换牌</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>消耗 1 张手牌，获得 6 金币。</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>获得 8 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="38" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>加码</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -3911,12 +3907,12 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点能量。每拥有 50 金币，额外 +1 点能量。</t>
+          <t>将任意张手牌放回抽牌堆，再抽等量的牌。</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>基础 2 能量</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -3932,176 +3928,177 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>换牌</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>回复 2 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="38" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>真赌</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>押牌</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>赌博·真赌</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>花费 5 金币。
+获得 2 点能量。硬币为正时：返还这 5 金币。</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>3 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>你每累计花费 6 金币，抽 1 张牌。</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>每累计 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>附加费</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>摸牌</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>将任意张手牌放回抽牌堆，再抽等量的牌。</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>费用变为 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>特异</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>分红</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>每回合开始支付 3 金币，回复 1 点生命。</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>回复 2 点生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="38" customHeight="1">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>真赌</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>单双</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>赌博·真赌</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>花费追踪</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>流水</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -4111,12 +4108,13 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>你每累计花费 6 金币，抽 1 张牌。</t>
+          <t>花费 4 金币。
+抽 2 张牌。</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>每累计 5 金币</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -4132,11 +4130,11 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>摸牌</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -4151,7 +4149,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>0能+4金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4161,13 +4159,13 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>花费 4 金币。
-抽 2 张牌。</t>
+          <t>花费 2 金币。
+获得 1 点能量。</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4179,20 +4177,20 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>附加费</t>
+          <t>风头·兑现</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>割禾青</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4202,23 +4200,22 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>0能+2金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>花费 2 金币。
-获得 1 点能量。</t>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>获得 2 点</t>
+          <t>至多 4 张</t>
         </is>
       </c>
     </row>
@@ -4234,16 +4231,16 @@
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4253,7 +4250,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4263,12 +4260,12 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）。结算后清空倍率。</t>
+          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>至多 4 张</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
@@ -4280,15 +4277,15 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>风头·兑现</t>
+          <t>风头·只读条件</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -4308,42 +4305,42 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>按倍率折算：获得「倍率取整」点能量，结算后清空倍率。</t>
+          <t>抽 3 张牌。若风头正盛倍率 ≥1.5，额外抽 2 张牌。</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>+1 点</t>
+          <t>额外抽 3 张牌</t>
         </is>
       </c>
     </row>
     <row r="75" ht="38" customHeight="1">
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>操控·辅助</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>风头·只读条件</t>
+          <t>做局</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>底牌</t>
+          <t>暗记</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4353,7 +4350,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4362,64 +4359,64 @@
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>做局</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>暗记</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>花费 2 金币。
 你的接下来 2 次赌博必为正面。</t>
         </is>
       </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>接下来 3 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>做局</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+        </is>
+      </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>接下来 3 次必为正面</t>
+          <t>+25%</t>
         </is>
       </c>
     </row>
@@ -4435,16 +4432,16 @@
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>手气正旺</t>
+          <t>赌神</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4454,7 +4451,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4464,12 +4461,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>赌博正面率 +15%（加法，上限 75%）。</t>
+          <t>你的所有赌博视为正面。</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>费用变为 2</t>
         </is>
       </c>
     </row>
@@ -4485,26 +4482,26 @@
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>赌神</t>
+          <t>叠码</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>3能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4514,12 +4511,12 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>你的所有赌博视为正面。</t>
+          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>费用变为 2</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
@@ -4535,16 +4532,16 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>出千</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -4564,12 +4561,12 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率 +0.5 ×2（不清空）。</t>
+          <t>你接下来的所有赌博必为正面（本回合）。</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4585,11 +4582,11 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -4604,7 +4601,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4614,12 +4611,12 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>你接下来的所有赌博必为正面（本回合）。</t>
+          <t>你的风头倍率翻倍（不清空）。</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4631,20 +4628,20 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>做局</t>
+          <t>出千·确定性</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>倍投</t>
+          <t>抽水</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4654,7 +4651,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4664,12 +4661,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>你的风头倍率翻倍（不清空）。</t>
+          <t>获得 2 次必正，以及 5 点活力。</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>3 次必正</t>
         </is>
       </c>
     </row>
@@ -4685,16 +4682,16 @@
         </is>
       </c>
       <c r="D82" s="11" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>封口</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4714,12 +4711,12 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>获得 2 次必正，以及 5 点活力。</t>
+          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>3 次必正</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -4735,76 +4732,76 @@
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>千王</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="38" customHeight="1">
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>出千·确定性</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。（升级：额外获得 2 次必正）</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>获得 2 次必正，抽 2 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>千王</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -4813,68 +4810,68 @@
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>每回合前 1 次掷出正面时，获得 1 次必正。</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="38" customHeight="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>操控·辅助</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>出千·确定性</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>瞒天过海</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>花费 6 金币。
 本回合你接下来的 3 次赌博必为正面。</t>
         </is>
       </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>操控·辅助</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>特异</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>你的接下来 1 次金币花费不消耗金币。</t>
+        </is>
+      </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>4 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
+          <t>本场战斗前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="38" customHeight="1">
       <c r="B86" s="5" t="inlineStr">
         <is>
           <t>操控·辅助</t>
@@ -4886,16 +4883,16 @@
         </is>
       </c>
       <c r="D86" s="11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -4915,12 +4912,12 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>你的接下来 1 次金币花费不消耗金币。</t>
+          <t>若风头倍率为偶数：获得 20 金币；若为奇数：获得 2 点力量与 2 点敏捷。</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>本场战斗前 2 次</t>
+          <t>26 金 / 3+3</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5104,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -5117,13 +5114,13 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-施加 5 点力量削弱与 3 易伤。</t>
+          <t>花费 4 金币。
+施加 6 点力量削弱与 4 易伤。</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>6 点力量削弱与 4 易伤</t>
+          <t>8 点力量削弱与 5 易伤</t>
         </is>
       </c>
     </row>
@@ -5341,10 +5338,10 @@
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>1</v>
@@ -5353,7 +5350,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" s="10" t="n">
         <v>1</v>
@@ -5363,11 +5360,9 @@
       <c r="O5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" s="10" t="n"/>
       <c r="Q5" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>2</v>
@@ -5376,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -5438,23 +5433,23 @@
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="P7" s="10" t="n"/>
       <c r="Q7" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R7" s="10" t="n"/>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5523,7 +5518,7 @@
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
       <c r="Q9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>4</v>
@@ -5532,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -5585,16 +5580,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4</v>
@@ -5612,10 +5607,10 @@
         <v>1</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R11" s="7" t="n">
         <v>6</v>
@@ -5631,7 +5626,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（俄罗斯轮盘、偷天换日、放血、翻本、抽头、割肉），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（偷天换日、放血、翻本、抽头、截胡、保本），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
         </is>
       </c>
     </row>
@@ -8213,11 +8208,11 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="54" customHeight="1">
+          <t>正面 55 / 反面 32</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="38" customHeight="1">
       <c r="B67" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8233,7 +8228,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -8243,17 +8238,17 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对随机敌人造成 !HeadsDamage! 伤害 5 次；硬币为负时：对随机敌人造成 3 伤害 3 次，且自己受到 10 伤害。</t>
+          <t>每回合开始随机开一枪：自己受到 3 点伤害并获得 5 金币，或对随机敌人造成 10 点伤害。</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>自己 2 伤+7 金 / 敌人 14 伤</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -8288,13 +8283,13 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 35 伤害。击杀则获得 25 金币。</t>
+          <t>花费 10 金币。
+造成 40 伤害。击杀则获得 30 金币。</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>40 伤害</t>
+          <t>46 伤害</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8314,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -8329,13 +8324,13 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>花费 12 金币。
-造成 43 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>花费 10 金币。
+造成 48 伤害。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>46 伤害</t>
+          <t>54 伤害</t>
         </is>
       </c>
     </row>
@@ -8365,17 +8360,17 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>赌博·真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 4 点能量；硬币为负时：失去 1 点能量。</t>
+          <t>若风头倍率为偶数：获得 20 金币；若为奇数：获得 2 点力量与 2 点敏捷。</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>26 金 / 3+3</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8395,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -8410,13 +8405,12 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-对生命值最低的敌人造成 43 伤害。</t>
+          <t>对生命值最低的敌人造成 15 伤害。若你的金币少于 100，伤害翻倍。</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>50 伤害</t>
+          <t>19 / 翻倍 38</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8435,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -8451,12 +8445,12 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>消耗。抽 2 张牌，获得 14 金币。</t>
+          <t>消耗。抽 2 张牌，获得 16 金币。</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>抽 3 张，20 金币</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8475,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -8491,13 +8485,13 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-施加 5 点力量削弱与 3 易伤。</t>
+          <t>花费 4 金币。
+施加 6 点力量削弱与 4 易伤。</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>6 点力量削弱与 4 易伤</t>
+          <t>8 点力量削弱与 5 易伤</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8516,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -8532,12 +8526,12 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若风头正盛倍率 ≥1.5，额外抽 1 张牌。</t>
+          <t>抽 3 张牌。若风头正盛倍率 ≥1.5，额外抽 2 张牌。</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>额外抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -8612,16 +8606,16 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币。</t>
+          <t>本场战斗中你每次获得金币时，额外获得 3 金币。</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="38" customHeight="1">
+          <t>额外 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
       <c r="B77" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8637,32 +8631,31 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>花费 15 金币。
-造成 50 伤害。数值随头顶倍率放大，结算后清空。</t>
+          <t>本场战斗中，你每次获得金币时，获得等量格挡。</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>62 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="54" customHeight="1">
+          <t>等量 +5 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="38" customHeight="1">
       <c r="B78" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8683,7 +8676,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -8693,17 +8686,16 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-造成 29 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
+          <t>造成 20 伤害。数值随头顶倍率放大；若击杀则倍率不清空。</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>36 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="38" customHeight="1">
+          <t>24 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
       <c r="B79" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8734,12 +8726,12 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡。格挡随头顶倍率放大，自身失去「倍率 ×3」生命，结算后清空。</t>
+          <t>获得 12 格挡。数值随头顶倍率放大，结算后清空。</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>15 格挡</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8767,7 @@
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>花费 7×X 金币。
-对随机敌人造成 9×X 伤害，共 X 次。</t>
+对随机敌人造成 12×X 伤害，共 X 次。</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -8805,7 +8797,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -8820,7 +8812,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8837,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -8855,16 +8847,16 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 20）。</t>
+          <t>对随机敌人造成等同于弃牌堆张数的伤害（至多 30）。</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>至多 28</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="38" customHeight="1">
+          <t>至多 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
       <c r="B83" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8880,12 +8872,12 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -8895,13 +8887,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>花费 10 金币。
-消耗你一半金币，获得等量格挡（至多 30）。</t>
+          <t>本场战斗中，你每花费 1 金币，获得 1 点敏捷。</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>每金 +1 力量 +1 敏捷</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8912,12 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -8936,16 +8927,17 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 8 伤害并弃掉 2 张手牌。</t>
+          <t>花费 5 金币。
+获得 2 点能量。硬币为正时：返还这 5 金币。</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="54" customHeight="1">
+          <t>3 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="38" customHeight="1">
       <c r="B85" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8961,12 +8953,12 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -8976,13 +8968,13 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>花费 8 金币。
-对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币。</t>
+          <t>花费 6 金币。
+获得 16 格挡，并获得等量金币。</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>20 格挡 / 20 金</t>
         </is>
       </c>
     </row>
@@ -9007,7 +8999,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -9022,7 +9014,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9079,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2能+18金</t>
+          <t>1能+9金</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -9097,13 +9089,13 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>花费 18 金币。
-造成 30 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
+          <t>花费 9 金币。
+造成 36 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>38 / 62</t>
+          <t>44 / 72</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -517,7 +517,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒卡池 · 功能分类总览（v1.8，78 张：起始 2 + 常规 76）</t>
+          <t>赌徒卡池 · 功能分类总览（v1.15，87 张：起始 2 + 常规 85）</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="J10" s="5" t="inlineStr">
         <is>
           <t>花费 5×X 金币。
-造成 27×X 伤害。</t>
+造成 20×X 伤害。</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>花费 9 金币。
-造成 36 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
+造成 36 伤害。若本场战斗中你掷出过正面，改为 60 伤害。</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>造成 6 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
+          <t>造成 6 伤害。若你的生命低于 50%，改为 14 伤害。</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>花费 10 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
+硬币为正时：造成 48 伤害；硬币为负时：造成 28 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
+硬币为正时：造成 30 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 13 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>硬币为正时：造成 10 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 20 伤害。</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+          <t>获得 7 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
+          <t>硬币为正时：获得 9 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -3504,7 +3504,7 @@
       <c r="J58" s="5" t="inlineStr">
         <is>
           <t>花费 3 金币。
-硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 10 格挡。</t>
+硬币为正时：获得 16 格挡；硬币为负时：获得 10 格挡。</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="70" customHeight="1">
+    <row r="59" ht="54" customHeight="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
@@ -3555,7 +3555,7 @@
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
-硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
+硬币为正时：获得 10 格挡并造成 10 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 5 伤害。</t>
+          <t>硬币为正时：造成 10 伤害；硬币为负时：造成 5 伤害。</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>硬币为正时：对所有敌人造成 !HeadsDamage! 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
+          <t>硬币为正时：对所有敌人造成 13 伤害；硬币为负时：对所有敌人造成 6 伤害。</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 5 格挡。</t>
+          <t>硬币为正时：获得 9 格挡；硬币为负时：获得 5 格挡。</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -6790,7 +6790,7 @@
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t>花费 5×X 金币。
-造成 27×X 伤害。</t>
+造成 20×X 伤害。</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 !HotDamage! 伤害。</t>
+          <t>造成 10 伤害。若风头正盛倍率 ≥1.5，改为造成 20 伤害。</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -7277,7 +7277,7 @@
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
-硬币为正时：获得 !HeadsBlock! 格挡；硬币为负时：获得 10 格挡。</t>
+硬币为正时：获得 16 格挡；硬币为负时：获得 10 格挡。</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>获得 !GoldGain! 金币（×倍率；结算后清空）。</t>
+          <t>获得 7 金币（×倍率；结算后清空）。</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -7720,7 +7720,7 @@
       <c r="H54" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
+硬币为正时：造成 30 伤害；硬币为负时：造成 18 伤害且自己失去 3 点生命。</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -7729,7 +7729,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="70" customHeight="1">
+    <row r="55" ht="54" customHeight="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
@@ -7761,7 +7761,7 @@
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t>花费 3 金币。
-硬币为正时：获得 !HeadsBlock! 格挡并造成 !HeadsDamage! 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
+硬币为正时：获得 10 格挡并造成 10 伤害；硬币为负时：获得 6 格挡并造成 6 伤害。</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>造成 6 伤害。若你的生命低于 50%，改为 !LowDamage! 伤害。</t>
+          <t>造成 6 伤害。若你的生命低于 50%，改为 14 伤害。</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -8203,7 +8203,7 @@
       <c r="H66" s="5" t="inlineStr">
         <is>
           <t>花费 10 金币。
-硬币为正时：造成 !HeadsDamage! 伤害；硬币为负时：造成 !TailsDamage! 伤害且自己受到 6 伤害。</t>
+硬币为正时：造成 48 伤害；硬币为负时：造成 28 伤害且自己受到 6 伤害。</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -9090,7 +9090,7 @@
       <c r="H88" s="5" t="inlineStr">
         <is>
           <t>花费 9 金币。
-造成 36 伤害。若本场战斗中你掷出过正面，改为 !HotDamage! 伤害。</t>
+造成 36 伤害。若本场战斗中你掷出过正面，改为 60 伤害。</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>抽税</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>打手</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>追击</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>捡漏</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>人头费</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>回收</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>清仓</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>保护费</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>截胡</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>存钱</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>留一手</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>记账</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>跟注</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>还手</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>护池</t>
+          <t>封盘</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>止损</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>典当</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>底气</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>充能</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>见好就收</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>提现</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>做手脚</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>发牌</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>假币</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>押注</t>
+          <t>拼命</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>重注</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>抽佣</t>
+          <t>暗算</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>口径：一张卡可同时带 2 个机制标签（偷天换日、放血、翻本、抽头、截胡、保本），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
+          <t>口径：一张卡可同时带 2 个机制标签（偷天换日、放血、翻本、抽头、过路费、保本），故机制列合计 93 &gt; 卡数 87；「合计」列为各功能族实际张数，总计 87。</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>打手</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>跟注</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>捡漏</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>人头费</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>抽税</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>记账</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>典当</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>护池</t>
+          <t>封盘</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>充能</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>发牌</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>重注</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>假币</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>保护费</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>见好就收</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>做手脚</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>还手</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>回收</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>底气</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>清仓</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>留一手</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>押注</t>
+          <t>拼命</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>抽佣</t>
+          <t>暗算</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>存钱</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>追击</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>止损</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>截胡</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>提现</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">

--- a/docs/design/gambler-cards-classified.xlsx
+++ b/docs/design/gambler-cards-classified.xlsx
@@ -3966,7 +3966,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="38" customHeight="1">
+    <row r="68" ht="54" customHeight="1">
       <c r="B68" s="5" t="inlineStr">
         <is>
           <t>资源</t>
@@ -4008,7 +4008,7 @@
       <c r="J68" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-获得 2 点能量。硬币为正时：返还这 5 金币。</t>
+获得 2 点能量。硬币为正时：返还这 5 金币；硬币为负时：不返还。</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -8896,7 +8896,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="38" customHeight="1">
+    <row r="84" ht="54" customHeight="1">
       <c r="B84" s="5" t="inlineStr">
         <is>
           <t>稀有</t>
@@ -8928,7 +8928,7 @@
       <c r="H84" s="5" t="inlineStr">
         <is>
           <t>花费 5 金币。
-获得 2 点能量。硬币为正时：返还这 5 金币。</t>
+获得 2 点能量。硬币为正时：返还这 5 金币；硬币为负时：不返还。</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
